--- a/data/OlimpiadData.xlsx
+++ b/data/OlimpiadData.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Арсений\PycharmProjects\HacathonMax\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Лист1" sheetId="1" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="130">
   <si>
     <t>№</t>
   </si>
@@ -25,9 +33,6 @@
     <t>Профиль</t>
   </si>
   <si>
-    <t>Классы</t>
-  </si>
-  <si>
     <t>Уровень (РСОШ)</t>
   </si>
   <si>
@@ -103,6 +108,9 @@
     <t>7–11</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>АНО ВО «Университет Иннополис»</t>
   </si>
   <si>
@@ -179,9 +187,6 @@
   </si>
   <si>
     <t>Отдельный сайт совместного профиля с 1С</t>
-  </si>
-  <si>
-    <t>Олимпиада школьников «Высшая проба»⁠</t>
   </si>
   <si>
     <t>vysshaya-proba-math-2026</t>
@@ -208,39 +213,286 @@
   <si>
     <t>Формат отбора: Дистанционный (онлайн в контест-системе).
  Формат финала: Очный (с использованием прокторинга)</t>
+  </si>
+  <si>
+    <t>Всесибирская открытая олимпиада</t>
+  </si>
+  <si>
+    <t>vsesibirskaya-informatika-2026</t>
+  </si>
+  <si>
+    <t>В проекте</t>
+  </si>
+  <si>
+    <t>Министерство образования Новосибирской области, ФГАОУ ВО «Новосибирский национальный исследовательский государственный университет» (НГУ)</t>
+  </si>
+  <si>
+    <t>https://sesc.nsu.ru/olymp-vsesib/sections/</t>
+  </si>
+  <si>
+    <t>19.10.2026 – 06.11.2026 (до 11:00 НСК)</t>
+  </si>
+  <si>
+    <t>08.11.2026 (в 11:00 НСК)</t>
+  </si>
+  <si>
+    <t>01.02.2027 – 19.02.2027 (до 11:00 НСК)</t>
+  </si>
+  <si>
+    <t>21.02.2027 (в 11:00 НСК)</t>
+  </si>
+  <si>
+    <t>Время начала туров — 11:00 по новосибирскому времени. Проводится в 2 этапа (отборочный и заключительный).</t>
+  </si>
+  <si>
+    <t>Международная олимпиада школьников  «Изумруд»</t>
+  </si>
+  <si>
+    <t>uzimrud-math-2026</t>
+  </si>
+  <si>
+    <t>8-11/СПО</t>
+  </si>
+  <si>
+    <t>Уральский федеральный университет (УрФУ) и Министерство образования Свердловской области</t>
+  </si>
+  <si>
+    <t>https://dovuz.urfu.ru/olymps/izumrud</t>
+  </si>
+  <si>
+    <t>01.09.2026 – 19.01.2027</t>
+  </si>
+  <si>
+    <t>20.01.2027 – 24.01.2027</t>
+  </si>
+  <si>
+    <t>30.01.2027 – 02.02.2027</t>
+  </si>
+  <si>
+    <t>Отбор онлайн. Финал очно (30.01 – 02.02.2027). Апелляции и проверка работ: 20.03.2027 в 12:00 (по Екатеринбургу). Итоги: 27.03.2027.</t>
+  </si>
+  <si>
+    <t>Олимпиада школьников «Шаг в будущее»</t>
+  </si>
+  <si>
+    <t>утверждена</t>
+  </si>
+  <si>
+    <t>МГТУ им. Н.Э. Баумана</t>
+  </si>
+  <si>
+    <t>https://olymp.bmstu.ru/ru</t>
+  </si>
+  <si>
+    <t>до 08.11.2026</t>
+  </si>
+  <si>
+    <t>16.11.2026 – 22.11.2026</t>
+  </si>
+  <si>
+    <t>анонсируется позже</t>
+  </si>
+  <si>
+    <t>Отборочный этап проходит очно на площадках (длительность 3 часа 55 минут).</t>
+  </si>
+  <si>
+    <t>Университетская олимпиада школьников «Бельчонок»</t>
+  </si>
+  <si>
+    <t>belchonok-informatics-2026</t>
+  </si>
+  <si>
+    <t>Сибирский федеральный университет (СФУ)</t>
+  </si>
+  <si>
+    <t>https://dovuz.sfu.ru/abiturientu-sfu/olimpiady/belchonok/2026-2027-uchebnyy-god/?ysclid=mumwbwr0vp811347530</t>
+  </si>
+  <si>
+    <t>01.10.2026 – 12.01.2027</t>
+  </si>
+  <si>
+    <t>Отборочный этап дистанционный (доступ до 17:00 по крск). Финал очный (Красноярск и региональные площадки).</t>
+  </si>
+  <si>
+    <t>Международная олимпиада школьников «Формула Единства» / «Третье тысячелетие»</t>
+  </si>
+  <si>
+    <t>formula-edinstva-math-2026</t>
+  </si>
+  <si>
+    <t>СПбГЭТУ «ЛЭТИ», РАНХиГС</t>
+  </si>
+  <si>
+    <t>https://www.formulo.org/ru/olymp/2026-math-ru/?ysclid=mumwutfvx421164466</t>
+  </si>
+  <si>
+    <t>до 05.11.2026</t>
+  </si>
+  <si>
+    <t>15.10.2026 – 05.11.2026</t>
+  </si>
+  <si>
+    <t>Автоматически по итогам отбора</t>
+  </si>
+  <si>
+    <t>Заочный отборочный тур (с применением дистанционных технологий). Финал очно на региональных площадках. Стратегический партнёр — ОЭЗ ППТ «Алабуга».</t>
+  </si>
+  <si>
+    <t>Олимпиада школьников «Гранит науки»</t>
+  </si>
+  <si>
+    <t>granit-nauki-informatics-2026</t>
+  </si>
+  <si>
+    <t>9-11/СПО</t>
+  </si>
+  <si>
+    <t>ФГБОУ ВО «Санкт-Петербургский горный университет императрицы Екатерины II».</t>
+  </si>
+  <si>
+    <t>https://ogn.spmi.ru/?ysclid=mumxdgle2352155733</t>
+  </si>
+  <si>
+    <t>05.10.2026 – 13.01.2027</t>
+  </si>
+  <si>
+    <t>Январь 2027</t>
+  </si>
+  <si>
+    <t>Отборочный тур проходит дистанционно/онлайн (05.10.2026 – 13.01.2027). Заключительный тур — 6 февраля 2027 года.</t>
+  </si>
+  <si>
+    <t>Всероссийская олимпиада школьников (ВсОШ) — Информатика</t>
+  </si>
+  <si>
+    <t>vsosh-informatics-school-2026</t>
+  </si>
+  <si>
+    <t>Минпросвещения России / Школа</t>
+  </si>
+  <si>
+    <t>https://sh2-cherlak-r52.gosweb.gosuslugi.ru/roditelyam-i-uchenikam/vserossiyskaya-olimpiada-shkolnikov/vserossiyskaya-olimpiada-shkolnikov-2026-2027/</t>
+  </si>
+  <si>
+    <t>Через классного руководителя / школу (сентябрь–октябрь 2026)</t>
+  </si>
+  <si>
+    <t>19.10.2026 , 21.10.2026 ,  22.10.2026 , 23.10.2026 (по направлениям)</t>
+  </si>
+  <si>
+    <t>По итогам проходных баллов на муниципальный этап</t>
+  </si>
+  <si>
+    <t>Ноябрь–Декабрь 2026 (муниципальный этап)</t>
+  </si>
+  <si>
+    <t>Школьный этап проходит онлайн с 8:00 до 22:00 по направлениям (ИИ, программирование, ИБ, робототехника)</t>
+  </si>
+  <si>
+    <t>Всероссийская олимпиада школьников (ВсОШ) — Математика</t>
+  </si>
+  <si>
+    <t>vsosh-math-school-2026</t>
+  </si>
+  <si>
+    <t>14.10.2026 (4-6 кл.), 16.10.2026 (7-11 кл.)</t>
+  </si>
+  <si>
+    <t>Автоматически при проходе на муниципальный этап</t>
+  </si>
+  <si>
+    <t>Школьный этап проходит в онлайн-формате (платформы «Сириус.Курсы» / МЭШ и др.) с 8:00 до 22:00.</t>
+  </si>
+  <si>
+    <t>Классы</t>
+  </si>
+  <si>
+    <t>Олимпиада школьников «Высшая проба»</t>
+  </si>
+  <si>
+    <t>shag_v_budushee-math-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="d.m.yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="164" formatCode="d\.m\.yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="13">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Montserrat"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
+      <color rgb="FF1A1B20"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <color rgb="FF1A1B20"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1A1B20"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF1A1B20"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A1B20"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1A1B20"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -248,7 +500,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -270,7 +522,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF73777E"/>
@@ -284,52 +542,95 @@
       <bottom style="thin">
         <color rgb="FF73777E"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -337,7 +638,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -527,31 +828,37 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:P998"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.75"/>
-    <col customWidth="1" min="2" max="2" width="15.88"/>
-    <col customWidth="1" min="3" max="4" width="11.63"/>
-    <col customWidth="1" min="5" max="5" width="10.63"/>
-    <col customWidth="1" min="6" max="7" width="10.75"/>
-    <col customWidth="1" min="8" max="8" width="15.13"/>
-    <col customWidth="1" min="9" max="9" width="12.13"/>
-    <col customWidth="1" min="10" max="10" width="16.75"/>
-    <col customWidth="1" min="11" max="13" width="16.63"/>
-    <col customWidth="1" min="14" max="14" width="15.75"/>
-    <col customWidth="1" min="15" max="15" width="16.25"/>
-    <col customWidth="1" min="16" max="16" width="18.38"/>
+    <col min="1" max="1" width="2.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="55.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="11" max="11" width="19.33203125" customWidth="1"/>
+    <col min="12" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="20.77734375" customWidth="1"/>
+    <col min="15" max="15" width="16.21875" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="64.2" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -564,366 +871,4714 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="4">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="6">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4" t="s">
+      <c r="M3" s="5"/>
+      <c r="N3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    <row r="4" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
+      <c r="M4" s="3"/>
+      <c r="N4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="P4" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4" t="s">
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="6">
-        <v>46306.0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>46327.0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>46333.0</v>
-      </c>
-      <c r="N5" s="4" t="s">
+      <c r="K5" s="8">
+        <v>46306</v>
+      </c>
+      <c r="L5" s="9">
+        <v>46327</v>
+      </c>
+      <c r="M5" s="9">
+        <v>46333</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="8">
-        <v>46432.0</v>
-      </c>
-      <c r="P5" s="4" t="s">
+      <c r="O5" s="10">
+        <v>46432</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="2" t="s">
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="s">
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="I7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A10" s="15">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E10" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="17">
+        <v>3</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="H10" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="M10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A11" s="15">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="17">
+        <v>3</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A12" s="15">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="17">
+        <v>3</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="O12" s="21">
+        <v>46432</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A13" s="15">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="17">
+        <v>2</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="O13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A14" s="15">
+        <v>13</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="17">
+        <v>2</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="O14" s="21">
+        <v>46424</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A15" s="15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="17">
+        <v>1</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="O15" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="64.2" customHeight="1">
+      <c r="A16" s="15">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="17">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="5:14" ht="13.2">
+      <c r="E17" s="22"/>
+      <c r="N17" s="22"/>
+    </row>
+    <row r="18" spans="5:14" ht="13.2">
+      <c r="E18" s="22"/>
+      <c r="N18" s="22"/>
+    </row>
+    <row r="19" spans="5:14" ht="13.2">
+      <c r="E19" s="22"/>
+      <c r="N19" s="22"/>
+    </row>
+    <row r="20" spans="5:14" ht="13.2">
+      <c r="E20" s="22"/>
+      <c r="N20" s="22"/>
+    </row>
+    <row r="21" spans="5:14" ht="13.2">
+      <c r="E21" s="22"/>
+      <c r="N21" s="22"/>
+    </row>
+    <row r="22" spans="5:14" ht="13.2">
+      <c r="E22" s="22"/>
+      <c r="N22" s="22"/>
+    </row>
+    <row r="23" spans="5:14" ht="13.2">
+      <c r="E23" s="22"/>
+      <c r="N23" s="22"/>
+    </row>
+    <row r="24" spans="5:14" ht="13.2">
+      <c r="E24" s="22"/>
+      <c r="N24" s="22"/>
+    </row>
+    <row r="25" spans="5:14" ht="13.2">
+      <c r="E25" s="22"/>
+      <c r="N25" s="22"/>
+    </row>
+    <row r="26" spans="5:14" ht="13.2">
+      <c r="E26" s="22"/>
+      <c r="N26" s="22"/>
+    </row>
+    <row r="27" spans="5:14" ht="13.2">
+      <c r="E27" s="22"/>
+      <c r="N27" s="22"/>
+    </row>
+    <row r="28" spans="5:14" ht="13.2">
+      <c r="E28" s="22"/>
+      <c r="N28" s="22"/>
+    </row>
+    <row r="29" spans="5:14" ht="13.2">
+      <c r="E29" s="22"/>
+      <c r="N29" s="22"/>
+    </row>
+    <row r="30" spans="5:14" ht="13.2">
+      <c r="E30" s="22"/>
+      <c r="N30" s="22"/>
+    </row>
+    <row r="31" spans="5:14" ht="13.2">
+      <c r="E31" s="22"/>
+      <c r="N31" s="22"/>
+    </row>
+    <row r="32" spans="5:14" ht="13.2">
+      <c r="E32" s="22"/>
+      <c r="N32" s="22"/>
+    </row>
+    <row r="33" spans="5:14" ht="13.2">
+      <c r="E33" s="22"/>
+      <c r="N33" s="22"/>
+    </row>
+    <row r="34" spans="5:14" ht="13.2">
+      <c r="E34" s="22"/>
+      <c r="N34" s="22"/>
+    </row>
+    <row r="35" spans="5:14" ht="13.2">
+      <c r="E35" s="22"/>
+      <c r="N35" s="22"/>
+    </row>
+    <row r="36" spans="5:14" ht="13.2">
+      <c r="E36" s="22"/>
+      <c r="N36" s="22"/>
+    </row>
+    <row r="37" spans="5:14" ht="13.2">
+      <c r="E37" s="22"/>
+      <c r="N37" s="22"/>
+    </row>
+    <row r="38" spans="5:14" ht="13.2">
+      <c r="E38" s="22"/>
+      <c r="N38" s="22"/>
+    </row>
+    <row r="39" spans="5:14" ht="13.2">
+      <c r="E39" s="22"/>
+      <c r="N39" s="22"/>
+    </row>
+    <row r="40" spans="5:14" ht="13.2">
+      <c r="E40" s="22"/>
+      <c r="N40" s="22"/>
+    </row>
+    <row r="41" spans="5:14" ht="13.2">
+      <c r="E41" s="22"/>
+      <c r="N41" s="22"/>
+    </row>
+    <row r="42" spans="5:14" ht="13.2">
+      <c r="E42" s="22"/>
+      <c r="N42" s="22"/>
+    </row>
+    <row r="43" spans="5:14" ht="13.2">
+      <c r="E43" s="22"/>
+      <c r="N43" s="22"/>
+    </row>
+    <row r="44" spans="5:14" ht="13.2">
+      <c r="E44" s="22"/>
+      <c r="N44" s="22"/>
+    </row>
+    <row r="45" spans="5:14" ht="13.2">
+      <c r="E45" s="22"/>
+      <c r="N45" s="22"/>
+    </row>
+    <row r="46" spans="5:14" ht="13.2">
+      <c r="E46" s="22"/>
+      <c r="N46" s="22"/>
+    </row>
+    <row r="47" spans="5:14" ht="13.2">
+      <c r="E47" s="22"/>
+      <c r="N47" s="22"/>
+    </row>
+    <row r="48" spans="5:14" ht="13.2">
+      <c r="E48" s="22"/>
+      <c r="N48" s="22"/>
+    </row>
+    <row r="49" spans="5:14" ht="13.2">
+      <c r="E49" s="22"/>
+      <c r="N49" s="22"/>
+    </row>
+    <row r="50" spans="5:14" ht="13.2">
+      <c r="E50" s="22"/>
+      <c r="N50" s="22"/>
+    </row>
+    <row r="51" spans="5:14" ht="13.2">
+      <c r="E51" s="22"/>
+      <c r="N51" s="22"/>
+    </row>
+    <row r="52" spans="5:14" ht="13.2">
+      <c r="E52" s="22"/>
+      <c r="N52" s="22"/>
+    </row>
+    <row r="53" spans="5:14" ht="13.2">
+      <c r="E53" s="22"/>
+      <c r="N53" s="22"/>
+    </row>
+    <row r="54" spans="5:14" ht="13.2">
+      <c r="E54" s="22"/>
+      <c r="N54" s="22"/>
+    </row>
+    <row r="55" spans="5:14" ht="13.2">
+      <c r="E55" s="22"/>
+      <c r="N55" s="22"/>
+    </row>
+    <row r="56" spans="5:14" ht="13.2">
+      <c r="E56" s="22"/>
+      <c r="N56" s="22"/>
+    </row>
+    <row r="57" spans="5:14" ht="13.2">
+      <c r="E57" s="22"/>
+      <c r="N57" s="22"/>
+    </row>
+    <row r="58" spans="5:14" ht="13.2">
+      <c r="E58" s="22"/>
+      <c r="N58" s="22"/>
+    </row>
+    <row r="59" spans="5:14" ht="13.2">
+      <c r="E59" s="22"/>
+      <c r="N59" s="22"/>
+    </row>
+    <row r="60" spans="5:14" ht="13.2">
+      <c r="E60" s="22"/>
+      <c r="N60" s="22"/>
+    </row>
+    <row r="61" spans="5:14" ht="13.2">
+      <c r="E61" s="22"/>
+      <c r="N61" s="22"/>
+    </row>
+    <row r="62" spans="5:14" ht="13.2">
+      <c r="E62" s="22"/>
+      <c r="N62" s="22"/>
+    </row>
+    <row r="63" spans="5:14" ht="13.2">
+      <c r="E63" s="22"/>
+      <c r="N63" s="22"/>
+    </row>
+    <row r="64" spans="5:14" ht="13.2">
+      <c r="E64" s="22"/>
+      <c r="N64" s="22"/>
+    </row>
+    <row r="65" spans="5:14" ht="13.2">
+      <c r="E65" s="22"/>
+      <c r="N65" s="22"/>
+    </row>
+    <row r="66" spans="5:14" ht="13.2">
+      <c r="E66" s="22"/>
+      <c r="N66" s="22"/>
+    </row>
+    <row r="67" spans="5:14" ht="13.2">
+      <c r="E67" s="22"/>
+      <c r="N67" s="22"/>
+    </row>
+    <row r="68" spans="5:14" ht="13.2">
+      <c r="E68" s="22"/>
+      <c r="N68" s="22"/>
+    </row>
+    <row r="69" spans="5:14" ht="13.2">
+      <c r="E69" s="22"/>
+      <c r="N69" s="22"/>
+    </row>
+    <row r="70" spans="5:14" ht="13.2">
+      <c r="E70" s="22"/>
+      <c r="N70" s="22"/>
+    </row>
+    <row r="71" spans="5:14" ht="13.2">
+      <c r="E71" s="22"/>
+      <c r="N71" s="22"/>
+    </row>
+    <row r="72" spans="5:14" ht="13.2">
+      <c r="E72" s="22"/>
+      <c r="N72" s="22"/>
+    </row>
+    <row r="73" spans="5:14" ht="13.2">
+      <c r="E73" s="22"/>
+      <c r="N73" s="22"/>
+    </row>
+    <row r="74" spans="5:14" ht="13.2">
+      <c r="E74" s="22"/>
+      <c r="N74" s="22"/>
+    </row>
+    <row r="75" spans="5:14" ht="13.2">
+      <c r="E75" s="22"/>
+      <c r="N75" s="22"/>
+    </row>
+    <row r="76" spans="5:14" ht="13.2">
+      <c r="E76" s="22"/>
+      <c r="N76" s="22"/>
+    </row>
+    <row r="77" spans="5:14" ht="13.2">
+      <c r="E77" s="22"/>
+      <c r="N77" s="22"/>
+    </row>
+    <row r="78" spans="5:14" ht="13.2">
+      <c r="E78" s="22"/>
+      <c r="N78" s="22"/>
+    </row>
+    <row r="79" spans="5:14" ht="13.2">
+      <c r="E79" s="22"/>
+      <c r="N79" s="22"/>
+    </row>
+    <row r="80" spans="5:14" ht="13.2">
+      <c r="E80" s="22"/>
+      <c r="N80" s="22"/>
+    </row>
+    <row r="81" spans="5:14" ht="13.2">
+      <c r="E81" s="22"/>
+      <c r="N81" s="22"/>
+    </row>
+    <row r="82" spans="5:14" ht="13.2">
+      <c r="E82" s="22"/>
+      <c r="N82" s="22"/>
+    </row>
+    <row r="83" spans="5:14" ht="13.2">
+      <c r="E83" s="22"/>
+      <c r="N83" s="22"/>
+    </row>
+    <row r="84" spans="5:14" ht="13.2">
+      <c r="E84" s="22"/>
+      <c r="N84" s="22"/>
+    </row>
+    <row r="85" spans="5:14" ht="13.2">
+      <c r="E85" s="22"/>
+      <c r="N85" s="22"/>
+    </row>
+    <row r="86" spans="5:14" ht="13.2">
+      <c r="E86" s="22"/>
+      <c r="N86" s="22"/>
+    </row>
+    <row r="87" spans="5:14" ht="13.2">
+      <c r="E87" s="22"/>
+      <c r="N87" s="22"/>
+    </row>
+    <row r="88" spans="5:14" ht="13.2">
+      <c r="E88" s="22"/>
+      <c r="N88" s="22"/>
+    </row>
+    <row r="89" spans="5:14" ht="13.2">
+      <c r="E89" s="22"/>
+      <c r="N89" s="22"/>
+    </row>
+    <row r="90" spans="5:14" ht="13.2">
+      <c r="E90" s="22"/>
+      <c r="N90" s="22"/>
+    </row>
+    <row r="91" spans="5:14" ht="13.2">
+      <c r="E91" s="22"/>
+      <c r="N91" s="22"/>
+    </row>
+    <row r="92" spans="5:14" ht="13.2">
+      <c r="E92" s="22"/>
+      <c r="N92" s="22"/>
+    </row>
+    <row r="93" spans="5:14" ht="13.2">
+      <c r="E93" s="22"/>
+      <c r="N93" s="22"/>
+    </row>
+    <row r="94" spans="5:14" ht="13.2">
+      <c r="E94" s="22"/>
+      <c r="N94" s="22"/>
+    </row>
+    <row r="95" spans="5:14" ht="13.2">
+      <c r="E95" s="22"/>
+      <c r="N95" s="22"/>
+    </row>
+    <row r="96" spans="5:14" ht="13.2">
+      <c r="E96" s="22"/>
+      <c r="N96" s="22"/>
+    </row>
+    <row r="97" spans="5:14" ht="13.2">
+      <c r="E97" s="22"/>
+      <c r="N97" s="22"/>
+    </row>
+    <row r="98" spans="5:14" ht="13.2">
+      <c r="E98" s="22"/>
+      <c r="N98" s="22"/>
+    </row>
+    <row r="99" spans="5:14" ht="13.2">
+      <c r="E99" s="22"/>
+      <c r="N99" s="22"/>
+    </row>
+    <row r="100" spans="5:14" ht="13.2">
+      <c r="E100" s="22"/>
+      <c r="N100" s="22"/>
+    </row>
+    <row r="101" spans="5:14" ht="13.2">
+      <c r="E101" s="22"/>
+      <c r="N101" s="22"/>
+    </row>
+    <row r="102" spans="5:14" ht="13.2">
+      <c r="E102" s="22"/>
+      <c r="N102" s="22"/>
+    </row>
+    <row r="103" spans="5:14" ht="13.2">
+      <c r="E103" s="22"/>
+      <c r="N103" s="22"/>
+    </row>
+    <row r="104" spans="5:14" ht="13.2">
+      <c r="E104" s="22"/>
+      <c r="N104" s="22"/>
+    </row>
+    <row r="105" spans="5:14" ht="13.2">
+      <c r="E105" s="22"/>
+      <c r="N105" s="22"/>
+    </row>
+    <row r="106" spans="5:14" ht="13.2">
+      <c r="E106" s="22"/>
+      <c r="N106" s="22"/>
+    </row>
+    <row r="107" spans="5:14" ht="13.2">
+      <c r="E107" s="22"/>
+      <c r="N107" s="22"/>
+    </row>
+    <row r="108" spans="5:14" ht="13.2">
+      <c r="E108" s="22"/>
+      <c r="N108" s="22"/>
+    </row>
+    <row r="109" spans="5:14" ht="13.2">
+      <c r="E109" s="22"/>
+      <c r="N109" s="22"/>
+    </row>
+    <row r="110" spans="5:14" ht="13.2">
+      <c r="E110" s="22"/>
+      <c r="N110" s="22"/>
+    </row>
+    <row r="111" spans="5:14" ht="13.2">
+      <c r="E111" s="22"/>
+      <c r="N111" s="22"/>
+    </row>
+    <row r="112" spans="5:14" ht="13.2">
+      <c r="E112" s="22"/>
+      <c r="N112" s="22"/>
+    </row>
+    <row r="113" spans="5:14" ht="13.2">
+      <c r="E113" s="22"/>
+      <c r="N113" s="22"/>
+    </row>
+    <row r="114" spans="5:14" ht="13.2">
+      <c r="E114" s="22"/>
+      <c r="N114" s="22"/>
+    </row>
+    <row r="115" spans="5:14" ht="13.2">
+      <c r="E115" s="22"/>
+      <c r="N115" s="22"/>
+    </row>
+    <row r="116" spans="5:14" ht="13.2">
+      <c r="E116" s="22"/>
+      <c r="N116" s="22"/>
+    </row>
+    <row r="117" spans="5:14" ht="13.2">
+      <c r="E117" s="22"/>
+      <c r="N117" s="22"/>
+    </row>
+    <row r="118" spans="5:14" ht="13.2">
+      <c r="E118" s="22"/>
+      <c r="N118" s="22"/>
+    </row>
+    <row r="119" spans="5:14" ht="13.2">
+      <c r="E119" s="22"/>
+      <c r="N119" s="22"/>
+    </row>
+    <row r="120" spans="5:14" ht="13.2">
+      <c r="E120" s="22"/>
+      <c r="N120" s="22"/>
+    </row>
+    <row r="121" spans="5:14" ht="13.2">
+      <c r="E121" s="22"/>
+      <c r="N121" s="22"/>
+    </row>
+    <row r="122" spans="5:14" ht="13.2">
+      <c r="E122" s="22"/>
+      <c r="N122" s="22"/>
+    </row>
+    <row r="123" spans="5:14" ht="13.2">
+      <c r="E123" s="22"/>
+      <c r="N123" s="22"/>
+    </row>
+    <row r="124" spans="5:14" ht="13.2">
+      <c r="E124" s="22"/>
+      <c r="N124" s="22"/>
+    </row>
+    <row r="125" spans="5:14" ht="13.2">
+      <c r="E125" s="22"/>
+      <c r="N125" s="22"/>
+    </row>
+    <row r="126" spans="5:14" ht="13.2">
+      <c r="E126" s="22"/>
+      <c r="N126" s="22"/>
+    </row>
+    <row r="127" spans="5:14" ht="13.2">
+      <c r="E127" s="22"/>
+      <c r="N127" s="22"/>
+    </row>
+    <row r="128" spans="5:14" ht="13.2">
+      <c r="E128" s="22"/>
+      <c r="N128" s="22"/>
+    </row>
+    <row r="129" spans="5:14" ht="13.2">
+      <c r="E129" s="22"/>
+      <c r="N129" s="22"/>
+    </row>
+    <row r="130" spans="5:14" ht="13.2">
+      <c r="E130" s="22"/>
+      <c r="N130" s="22"/>
+    </row>
+    <row r="131" spans="5:14" ht="13.2">
+      <c r="E131" s="22"/>
+      <c r="N131" s="22"/>
+    </row>
+    <row r="132" spans="5:14" ht="13.2">
+      <c r="E132" s="22"/>
+      <c r="N132" s="22"/>
+    </row>
+    <row r="133" spans="5:14" ht="13.2">
+      <c r="E133" s="22"/>
+      <c r="N133" s="22"/>
+    </row>
+    <row r="134" spans="5:14" ht="13.2">
+      <c r="E134" s="22"/>
+      <c r="N134" s="22"/>
+    </row>
+    <row r="135" spans="5:14" ht="13.2">
+      <c r="E135" s="22"/>
+      <c r="N135" s="22"/>
+    </row>
+    <row r="136" spans="5:14" ht="13.2">
+      <c r="E136" s="22"/>
+      <c r="N136" s="22"/>
+    </row>
+    <row r="137" spans="5:14" ht="13.2">
+      <c r="E137" s="22"/>
+      <c r="N137" s="22"/>
+    </row>
+    <row r="138" spans="5:14" ht="13.2">
+      <c r="E138" s="22"/>
+      <c r="N138" s="22"/>
+    </row>
+    <row r="139" spans="5:14" ht="13.2">
+      <c r="E139" s="22"/>
+      <c r="N139" s="22"/>
+    </row>
+    <row r="140" spans="5:14" ht="13.2">
+      <c r="E140" s="22"/>
+      <c r="N140" s="22"/>
+    </row>
+    <row r="141" spans="5:14" ht="13.2">
+      <c r="E141" s="22"/>
+      <c r="N141" s="22"/>
+    </row>
+    <row r="142" spans="5:14" ht="13.2">
+      <c r="E142" s="22"/>
+      <c r="N142" s="22"/>
+    </row>
+    <row r="143" spans="5:14" ht="13.2">
+      <c r="E143" s="22"/>
+      <c r="N143" s="22"/>
+    </row>
+    <row r="144" spans="5:14" ht="13.2">
+      <c r="E144" s="22"/>
+      <c r="N144" s="22"/>
+    </row>
+    <row r="145" spans="5:14" ht="13.2">
+      <c r="E145" s="22"/>
+      <c r="N145" s="22"/>
+    </row>
+    <row r="146" spans="5:14" ht="13.2">
+      <c r="E146" s="22"/>
+      <c r="N146" s="22"/>
+    </row>
+    <row r="147" spans="5:14" ht="13.2">
+      <c r="E147" s="22"/>
+      <c r="N147" s="22"/>
+    </row>
+    <row r="148" spans="5:14" ht="13.2">
+      <c r="E148" s="22"/>
+      <c r="N148" s="22"/>
+    </row>
+    <row r="149" spans="5:14" ht="13.2">
+      <c r="E149" s="22"/>
+      <c r="N149" s="22"/>
+    </row>
+    <row r="150" spans="5:14" ht="13.2">
+      <c r="E150" s="22"/>
+      <c r="N150" s="22"/>
+    </row>
+    <row r="151" spans="5:14" ht="13.2">
+      <c r="E151" s="22"/>
+      <c r="N151" s="22"/>
+    </row>
+    <row r="152" spans="5:14" ht="13.2">
+      <c r="E152" s="22"/>
+      <c r="N152" s="22"/>
+    </row>
+    <row r="153" spans="5:14" ht="13.2">
+      <c r="E153" s="22"/>
+      <c r="N153" s="22"/>
+    </row>
+    <row r="154" spans="5:14" ht="13.2">
+      <c r="E154" s="22"/>
+      <c r="N154" s="22"/>
+    </row>
+    <row r="155" spans="5:14" ht="13.2">
+      <c r="E155" s="22"/>
+      <c r="N155" s="22"/>
+    </row>
+    <row r="156" spans="5:14" ht="13.2">
+      <c r="E156" s="22"/>
+      <c r="N156" s="22"/>
+    </row>
+    <row r="157" spans="5:14" ht="13.2">
+      <c r="E157" s="22"/>
+      <c r="N157" s="22"/>
+    </row>
+    <row r="158" spans="5:14" ht="13.2">
+      <c r="E158" s="22"/>
+      <c r="N158" s="22"/>
+    </row>
+    <row r="159" spans="5:14" ht="13.2">
+      <c r="E159" s="22"/>
+      <c r="N159" s="22"/>
+    </row>
+    <row r="160" spans="5:14" ht="13.2">
+      <c r="E160" s="22"/>
+      <c r="N160" s="22"/>
+    </row>
+    <row r="161" spans="5:14" ht="13.2">
+      <c r="E161" s="22"/>
+      <c r="N161" s="22"/>
+    </row>
+    <row r="162" spans="5:14" ht="13.2">
+      <c r="E162" s="22"/>
+      <c r="N162" s="22"/>
+    </row>
+    <row r="163" spans="5:14" ht="13.2">
+      <c r="E163" s="22"/>
+      <c r="N163" s="22"/>
+    </row>
+    <row r="164" spans="5:14" ht="13.2">
+      <c r="E164" s="22"/>
+      <c r="N164" s="22"/>
+    </row>
+    <row r="165" spans="5:14" ht="13.2">
+      <c r="E165" s="22"/>
+      <c r="N165" s="22"/>
+    </row>
+    <row r="166" spans="5:14" ht="13.2">
+      <c r="E166" s="22"/>
+      <c r="N166" s="22"/>
+    </row>
+    <row r="167" spans="5:14" ht="13.2">
+      <c r="E167" s="22"/>
+      <c r="N167" s="22"/>
+    </row>
+    <row r="168" spans="5:14" ht="13.2">
+      <c r="E168" s="22"/>
+      <c r="N168" s="22"/>
+    </row>
+    <row r="169" spans="5:14" ht="13.2">
+      <c r="E169" s="22"/>
+      <c r="N169" s="22"/>
+    </row>
+    <row r="170" spans="5:14" ht="13.2">
+      <c r="E170" s="22"/>
+      <c r="N170" s="22"/>
+    </row>
+    <row r="171" spans="5:14" ht="13.2">
+      <c r="E171" s="22"/>
+      <c r="N171" s="22"/>
+    </row>
+    <row r="172" spans="5:14" ht="13.2">
+      <c r="E172" s="22"/>
+      <c r="N172" s="22"/>
+    </row>
+    <row r="173" spans="5:14" ht="13.2">
+      <c r="E173" s="22"/>
+      <c r="N173" s="22"/>
+    </row>
+    <row r="174" spans="5:14" ht="13.2">
+      <c r="E174" s="22"/>
+      <c r="N174" s="22"/>
+    </row>
+    <row r="175" spans="5:14" ht="13.2">
+      <c r="E175" s="22"/>
+      <c r="N175" s="22"/>
+    </row>
+    <row r="176" spans="5:14" ht="13.2">
+      <c r="E176" s="22"/>
+      <c r="N176" s="22"/>
+    </row>
+    <row r="177" spans="5:14" ht="13.2">
+      <c r="E177" s="22"/>
+      <c r="N177" s="22"/>
+    </row>
+    <row r="178" spans="5:14" ht="13.2">
+      <c r="E178" s="22"/>
+      <c r="N178" s="22"/>
+    </row>
+    <row r="179" spans="5:14" ht="13.2">
+      <c r="E179" s="22"/>
+      <c r="N179" s="22"/>
+    </row>
+    <row r="180" spans="5:14" ht="13.2">
+      <c r="E180" s="22"/>
+      <c r="N180" s="22"/>
+    </row>
+    <row r="181" spans="5:14" ht="13.2">
+      <c r="E181" s="22"/>
+      <c r="N181" s="22"/>
+    </row>
+    <row r="182" spans="5:14" ht="13.2">
+      <c r="E182" s="22"/>
+      <c r="N182" s="22"/>
+    </row>
+    <row r="183" spans="5:14" ht="13.2">
+      <c r="E183" s="22"/>
+      <c r="N183" s="22"/>
+    </row>
+    <row r="184" spans="5:14" ht="13.2">
+      <c r="E184" s="22"/>
+      <c r="N184" s="22"/>
+    </row>
+    <row r="185" spans="5:14" ht="13.2">
+      <c r="E185" s="22"/>
+      <c r="N185" s="22"/>
+    </row>
+    <row r="186" spans="5:14" ht="13.2">
+      <c r="E186" s="22"/>
+      <c r="N186" s="22"/>
+    </row>
+    <row r="187" spans="5:14" ht="13.2">
+      <c r="E187" s="22"/>
+      <c r="N187" s="22"/>
+    </row>
+    <row r="188" spans="5:14" ht="13.2">
+      <c r="E188" s="22"/>
+      <c r="N188" s="22"/>
+    </row>
+    <row r="189" spans="5:14" ht="13.2">
+      <c r="E189" s="22"/>
+      <c r="N189" s="22"/>
+    </row>
+    <row r="190" spans="5:14" ht="13.2">
+      <c r="E190" s="22"/>
+      <c r="N190" s="22"/>
+    </row>
+    <row r="191" spans="5:14" ht="13.2">
+      <c r="E191" s="22"/>
+      <c r="N191" s="22"/>
+    </row>
+    <row r="192" spans="5:14" ht="13.2">
+      <c r="E192" s="22"/>
+      <c r="N192" s="22"/>
+    </row>
+    <row r="193" spans="5:14" ht="13.2">
+      <c r="E193" s="22"/>
+      <c r="N193" s="22"/>
+    </row>
+    <row r="194" spans="5:14" ht="13.2">
+      <c r="E194" s="22"/>
+      <c r="N194" s="22"/>
+    </row>
+    <row r="195" spans="5:14" ht="13.2">
+      <c r="E195" s="22"/>
+      <c r="N195" s="22"/>
+    </row>
+    <row r="196" spans="5:14" ht="13.2">
+      <c r="E196" s="22"/>
+      <c r="N196" s="22"/>
+    </row>
+    <row r="197" spans="5:14" ht="13.2">
+      <c r="E197" s="22"/>
+      <c r="N197" s="22"/>
+    </row>
+    <row r="198" spans="5:14" ht="13.2">
+      <c r="E198" s="22"/>
+      <c r="N198" s="22"/>
+    </row>
+    <row r="199" spans="5:14" ht="13.2">
+      <c r="E199" s="22"/>
+      <c r="N199" s="22"/>
+    </row>
+    <row r="200" spans="5:14" ht="13.2">
+      <c r="E200" s="22"/>
+      <c r="N200" s="22"/>
+    </row>
+    <row r="201" spans="5:14" ht="13.2">
+      <c r="E201" s="22"/>
+      <c r="N201" s="22"/>
+    </row>
+    <row r="202" spans="5:14" ht="13.2">
+      <c r="E202" s="22"/>
+      <c r="N202" s="22"/>
+    </row>
+    <row r="203" spans="5:14" ht="13.2">
+      <c r="E203" s="22"/>
+      <c r="N203" s="22"/>
+    </row>
+    <row r="204" spans="5:14" ht="13.2">
+      <c r="E204" s="22"/>
+      <c r="N204" s="22"/>
+    </row>
+    <row r="205" spans="5:14" ht="13.2">
+      <c r="E205" s="22"/>
+      <c r="N205" s="22"/>
+    </row>
+    <row r="206" spans="5:14" ht="13.2">
+      <c r="E206" s="22"/>
+      <c r="N206" s="22"/>
+    </row>
+    <row r="207" spans="5:14" ht="13.2">
+      <c r="E207" s="22"/>
+      <c r="N207" s="22"/>
+    </row>
+    <row r="208" spans="5:14" ht="13.2">
+      <c r="E208" s="22"/>
+      <c r="N208" s="22"/>
+    </row>
+    <row r="209" spans="5:14" ht="13.2">
+      <c r="E209" s="22"/>
+      <c r="N209" s="22"/>
+    </row>
+    <row r="210" spans="5:14" ht="13.2">
+      <c r="E210" s="22"/>
+      <c r="N210" s="22"/>
+    </row>
+    <row r="211" spans="5:14" ht="13.2">
+      <c r="E211" s="22"/>
+      <c r="N211" s="22"/>
+    </row>
+    <row r="212" spans="5:14" ht="13.2">
+      <c r="E212" s="22"/>
+      <c r="N212" s="22"/>
+    </row>
+    <row r="213" spans="5:14" ht="13.2">
+      <c r="E213" s="22"/>
+      <c r="N213" s="22"/>
+    </row>
+    <row r="214" spans="5:14" ht="13.2">
+      <c r="E214" s="22"/>
+      <c r="N214" s="22"/>
+    </row>
+    <row r="215" spans="5:14" ht="13.2">
+      <c r="E215" s="22"/>
+      <c r="N215" s="22"/>
+    </row>
+    <row r="216" spans="5:14" ht="13.2">
+      <c r="E216" s="22"/>
+      <c r="N216" s="22"/>
+    </row>
+    <row r="217" spans="5:14" ht="13.2">
+      <c r="E217" s="22"/>
+      <c r="N217" s="22"/>
+    </row>
+    <row r="218" spans="5:14" ht="13.2">
+      <c r="E218" s="22"/>
+      <c r="N218" s="22"/>
+    </row>
+    <row r="219" spans="5:14" ht="13.2">
+      <c r="E219" s="22"/>
+      <c r="N219" s="22"/>
+    </row>
+    <row r="220" spans="5:14" ht="13.2">
+      <c r="E220" s="22"/>
+      <c r="N220" s="22"/>
+    </row>
+    <row r="221" spans="5:14" ht="13.2">
+      <c r="E221" s="22"/>
+      <c r="N221" s="22"/>
+    </row>
+    <row r="222" spans="5:14" ht="13.2">
+      <c r="E222" s="22"/>
+      <c r="N222" s="22"/>
+    </row>
+    <row r="223" spans="5:14" ht="13.2">
+      <c r="E223" s="22"/>
+      <c r="N223" s="22"/>
+    </row>
+    <row r="224" spans="5:14" ht="13.2">
+      <c r="E224" s="22"/>
+      <c r="N224" s="22"/>
+    </row>
+    <row r="225" spans="5:14" ht="13.2">
+      <c r="E225" s="22"/>
+      <c r="N225" s="22"/>
+    </row>
+    <row r="226" spans="5:14" ht="13.2">
+      <c r="E226" s="22"/>
+      <c r="N226" s="22"/>
+    </row>
+    <row r="227" spans="5:14" ht="13.2">
+      <c r="E227" s="22"/>
+      <c r="N227" s="22"/>
+    </row>
+    <row r="228" spans="5:14" ht="13.2">
+      <c r="E228" s="22"/>
+      <c r="N228" s="22"/>
+    </row>
+    <row r="229" spans="5:14" ht="13.2">
+      <c r="E229" s="22"/>
+      <c r="N229" s="22"/>
+    </row>
+    <row r="230" spans="5:14" ht="13.2">
+      <c r="E230" s="22"/>
+      <c r="N230" s="22"/>
+    </row>
+    <row r="231" spans="5:14" ht="13.2">
+      <c r="E231" s="22"/>
+      <c r="N231" s="22"/>
+    </row>
+    <row r="232" spans="5:14" ht="13.2">
+      <c r="E232" s="22"/>
+      <c r="N232" s="22"/>
+    </row>
+    <row r="233" spans="5:14" ht="13.2">
+      <c r="E233" s="22"/>
+      <c r="N233" s="22"/>
+    </row>
+    <row r="234" spans="5:14" ht="13.2">
+      <c r="E234" s="22"/>
+      <c r="N234" s="22"/>
+    </row>
+    <row r="235" spans="5:14" ht="13.2">
+      <c r="E235" s="22"/>
+      <c r="N235" s="22"/>
+    </row>
+    <row r="236" spans="5:14" ht="13.2">
+      <c r="E236" s="22"/>
+      <c r="N236" s="22"/>
+    </row>
+    <row r="237" spans="5:14" ht="13.2">
+      <c r="E237" s="22"/>
+      <c r="N237" s="22"/>
+    </row>
+    <row r="238" spans="5:14" ht="13.2">
+      <c r="E238" s="22"/>
+      <c r="N238" s="22"/>
+    </row>
+    <row r="239" spans="5:14" ht="13.2">
+      <c r="E239" s="22"/>
+      <c r="N239" s="22"/>
+    </row>
+    <row r="240" spans="5:14" ht="13.2">
+      <c r="E240" s="22"/>
+      <c r="N240" s="22"/>
+    </row>
+    <row r="241" spans="5:14" ht="13.2">
+      <c r="E241" s="22"/>
+      <c r="N241" s="22"/>
+    </row>
+    <row r="242" spans="5:14" ht="13.2">
+      <c r="E242" s="22"/>
+      <c r="N242" s="22"/>
+    </row>
+    <row r="243" spans="5:14" ht="13.2">
+      <c r="E243" s="22"/>
+      <c r="N243" s="22"/>
+    </row>
+    <row r="244" spans="5:14" ht="13.2">
+      <c r="E244" s="22"/>
+      <c r="N244" s="22"/>
+    </row>
+    <row r="245" spans="5:14" ht="13.2">
+      <c r="E245" s="22"/>
+      <c r="N245" s="22"/>
+    </row>
+    <row r="246" spans="5:14" ht="13.2">
+      <c r="E246" s="22"/>
+      <c r="N246" s="22"/>
+    </row>
+    <row r="247" spans="5:14" ht="13.2">
+      <c r="E247" s="22"/>
+      <c r="N247" s="22"/>
+    </row>
+    <row r="248" spans="5:14" ht="13.2">
+      <c r="E248" s="22"/>
+      <c r="N248" s="22"/>
+    </row>
+    <row r="249" spans="5:14" ht="13.2">
+      <c r="E249" s="22"/>
+      <c r="N249" s="22"/>
+    </row>
+    <row r="250" spans="5:14" ht="13.2">
+      <c r="E250" s="22"/>
+      <c r="N250" s="22"/>
+    </row>
+    <row r="251" spans="5:14" ht="13.2">
+      <c r="E251" s="22"/>
+      <c r="N251" s="22"/>
+    </row>
+    <row r="252" spans="5:14" ht="13.2">
+      <c r="E252" s="22"/>
+      <c r="N252" s="22"/>
+    </row>
+    <row r="253" spans="5:14" ht="13.2">
+      <c r="E253" s="22"/>
+      <c r="N253" s="22"/>
+    </row>
+    <row r="254" spans="5:14" ht="13.2">
+      <c r="E254" s="22"/>
+      <c r="N254" s="22"/>
+    </row>
+    <row r="255" spans="5:14" ht="13.2">
+      <c r="E255" s="22"/>
+      <c r="N255" s="22"/>
+    </row>
+    <row r="256" spans="5:14" ht="13.2">
+      <c r="E256" s="22"/>
+      <c r="N256" s="22"/>
+    </row>
+    <row r="257" spans="5:14" ht="13.2">
+      <c r="E257" s="22"/>
+      <c r="N257" s="22"/>
+    </row>
+    <row r="258" spans="5:14" ht="13.2">
+      <c r="E258" s="22"/>
+      <c r="N258" s="22"/>
+    </row>
+    <row r="259" spans="5:14" ht="13.2">
+      <c r="E259" s="22"/>
+      <c r="N259" s="22"/>
+    </row>
+    <row r="260" spans="5:14" ht="13.2">
+      <c r="E260" s="22"/>
+      <c r="N260" s="22"/>
+    </row>
+    <row r="261" spans="5:14" ht="13.2">
+      <c r="E261" s="22"/>
+      <c r="N261" s="22"/>
+    </row>
+    <row r="262" spans="5:14" ht="13.2">
+      <c r="E262" s="22"/>
+      <c r="N262" s="22"/>
+    </row>
+    <row r="263" spans="5:14" ht="13.2">
+      <c r="E263" s="22"/>
+      <c r="N263" s="22"/>
+    </row>
+    <row r="264" spans="5:14" ht="13.2">
+      <c r="E264" s="22"/>
+      <c r="N264" s="22"/>
+    </row>
+    <row r="265" spans="5:14" ht="13.2">
+      <c r="E265" s="22"/>
+      <c r="N265" s="22"/>
+    </row>
+    <row r="266" spans="5:14" ht="13.2">
+      <c r="E266" s="22"/>
+      <c r="N266" s="22"/>
+    </row>
+    <row r="267" spans="5:14" ht="13.2">
+      <c r="E267" s="22"/>
+      <c r="N267" s="22"/>
+    </row>
+    <row r="268" spans="5:14" ht="13.2">
+      <c r="E268" s="22"/>
+      <c r="N268" s="22"/>
+    </row>
+    <row r="269" spans="5:14" ht="13.2">
+      <c r="E269" s="22"/>
+      <c r="N269" s="22"/>
+    </row>
+    <row r="270" spans="5:14" ht="13.2">
+      <c r="E270" s="22"/>
+      <c r="N270" s="22"/>
+    </row>
+    <row r="271" spans="5:14" ht="13.2">
+      <c r="E271" s="22"/>
+      <c r="N271" s="22"/>
+    </row>
+    <row r="272" spans="5:14" ht="13.2">
+      <c r="E272" s="22"/>
+      <c r="N272" s="22"/>
+    </row>
+    <row r="273" spans="5:14" ht="13.2">
+      <c r="E273" s="22"/>
+      <c r="N273" s="22"/>
+    </row>
+    <row r="274" spans="5:14" ht="13.2">
+      <c r="E274" s="22"/>
+      <c r="N274" s="22"/>
+    </row>
+    <row r="275" spans="5:14" ht="13.2">
+      <c r="E275" s="22"/>
+      <c r="N275" s="22"/>
+    </row>
+    <row r="276" spans="5:14" ht="13.2">
+      <c r="E276" s="22"/>
+      <c r="N276" s="22"/>
+    </row>
+    <row r="277" spans="5:14" ht="13.2">
+      <c r="E277" s="22"/>
+      <c r="N277" s="22"/>
+    </row>
+    <row r="278" spans="5:14" ht="13.2">
+      <c r="E278" s="22"/>
+      <c r="N278" s="22"/>
+    </row>
+    <row r="279" spans="5:14" ht="13.2">
+      <c r="E279" s="22"/>
+      <c r="N279" s="22"/>
+    </row>
+    <row r="280" spans="5:14" ht="13.2">
+      <c r="E280" s="22"/>
+      <c r="N280" s="22"/>
+    </row>
+    <row r="281" spans="5:14" ht="13.2">
+      <c r="E281" s="22"/>
+      <c r="N281" s="22"/>
+    </row>
+    <row r="282" spans="5:14" ht="13.2">
+      <c r="E282" s="22"/>
+      <c r="N282" s="22"/>
+    </row>
+    <row r="283" spans="5:14" ht="13.2">
+      <c r="E283" s="22"/>
+      <c r="N283" s="22"/>
+    </row>
+    <row r="284" spans="5:14" ht="13.2">
+      <c r="E284" s="22"/>
+      <c r="N284" s="22"/>
+    </row>
+    <row r="285" spans="5:14" ht="13.2">
+      <c r="E285" s="22"/>
+      <c r="N285" s="22"/>
+    </row>
+    <row r="286" spans="5:14" ht="13.2">
+      <c r="E286" s="22"/>
+      <c r="N286" s="22"/>
+    </row>
+    <row r="287" spans="5:14" ht="13.2">
+      <c r="E287" s="22"/>
+      <c r="N287" s="22"/>
+    </row>
+    <row r="288" spans="5:14" ht="13.2">
+      <c r="E288" s="22"/>
+      <c r="N288" s="22"/>
+    </row>
+    <row r="289" spans="5:14" ht="13.2">
+      <c r="E289" s="22"/>
+      <c r="N289" s="22"/>
+    </row>
+    <row r="290" spans="5:14" ht="13.2">
+      <c r="E290" s="22"/>
+      <c r="N290" s="22"/>
+    </row>
+    <row r="291" spans="5:14" ht="13.2">
+      <c r="E291" s="22"/>
+      <c r="N291" s="22"/>
+    </row>
+    <row r="292" spans="5:14" ht="13.2">
+      <c r="E292" s="22"/>
+      <c r="N292" s="22"/>
+    </row>
+    <row r="293" spans="5:14" ht="13.2">
+      <c r="E293" s="22"/>
+      <c r="N293" s="22"/>
+    </row>
+    <row r="294" spans="5:14" ht="13.2">
+      <c r="E294" s="22"/>
+      <c r="N294" s="22"/>
+    </row>
+    <row r="295" spans="5:14" ht="13.2">
+      <c r="E295" s="22"/>
+      <c r="N295" s="22"/>
+    </row>
+    <row r="296" spans="5:14" ht="13.2">
+      <c r="E296" s="22"/>
+      <c r="N296" s="22"/>
+    </row>
+    <row r="297" spans="5:14" ht="13.2">
+      <c r="E297" s="22"/>
+      <c r="N297" s="22"/>
+    </row>
+    <row r="298" spans="5:14" ht="13.2">
+      <c r="E298" s="22"/>
+      <c r="N298" s="22"/>
+    </row>
+    <row r="299" spans="5:14" ht="13.2">
+      <c r="E299" s="22"/>
+      <c r="N299" s="22"/>
+    </row>
+    <row r="300" spans="5:14" ht="13.2">
+      <c r="E300" s="22"/>
+      <c r="N300" s="22"/>
+    </row>
+    <row r="301" spans="5:14" ht="13.2">
+      <c r="E301" s="22"/>
+      <c r="N301" s="22"/>
+    </row>
+    <row r="302" spans="5:14" ht="13.2">
+      <c r="E302" s="22"/>
+      <c r="N302" s="22"/>
+    </row>
+    <row r="303" spans="5:14" ht="13.2">
+      <c r="E303" s="22"/>
+      <c r="N303" s="22"/>
+    </row>
+    <row r="304" spans="5:14" ht="13.2">
+      <c r="E304" s="22"/>
+      <c r="N304" s="22"/>
+    </row>
+    <row r="305" spans="5:14" ht="13.2">
+      <c r="E305" s="22"/>
+      <c r="N305" s="22"/>
+    </row>
+    <row r="306" spans="5:14" ht="13.2">
+      <c r="E306" s="22"/>
+      <c r="N306" s="22"/>
+    </row>
+    <row r="307" spans="5:14" ht="13.2">
+      <c r="E307" s="22"/>
+      <c r="N307" s="22"/>
+    </row>
+    <row r="308" spans="5:14" ht="13.2">
+      <c r="E308" s="22"/>
+      <c r="N308" s="22"/>
+    </row>
+    <row r="309" spans="5:14" ht="13.2">
+      <c r="E309" s="22"/>
+      <c r="N309" s="22"/>
+    </row>
+    <row r="310" spans="5:14" ht="13.2">
+      <c r="E310" s="22"/>
+      <c r="N310" s="22"/>
+    </row>
+    <row r="311" spans="5:14" ht="13.2">
+      <c r="E311" s="22"/>
+      <c r="N311" s="22"/>
+    </row>
+    <row r="312" spans="5:14" ht="13.2">
+      <c r="E312" s="22"/>
+      <c r="N312" s="22"/>
+    </row>
+    <row r="313" spans="5:14" ht="13.2">
+      <c r="E313" s="22"/>
+      <c r="N313" s="22"/>
+    </row>
+    <row r="314" spans="5:14" ht="13.2">
+      <c r="E314" s="22"/>
+      <c r="N314" s="22"/>
+    </row>
+    <row r="315" spans="5:14" ht="13.2">
+      <c r="E315" s="22"/>
+      <c r="N315" s="22"/>
+    </row>
+    <row r="316" spans="5:14" ht="13.2">
+      <c r="E316" s="22"/>
+      <c r="N316" s="22"/>
+    </row>
+    <row r="317" spans="5:14" ht="13.2">
+      <c r="E317" s="22"/>
+      <c r="N317" s="22"/>
+    </row>
+    <row r="318" spans="5:14" ht="13.2">
+      <c r="E318" s="22"/>
+      <c r="N318" s="22"/>
+    </row>
+    <row r="319" spans="5:14" ht="13.2">
+      <c r="E319" s="22"/>
+      <c r="N319" s="22"/>
+    </row>
+    <row r="320" spans="5:14" ht="13.2">
+      <c r="E320" s="22"/>
+      <c r="N320" s="22"/>
+    </row>
+    <row r="321" spans="5:14" ht="13.2">
+      <c r="E321" s="22"/>
+      <c r="N321" s="22"/>
+    </row>
+    <row r="322" spans="5:14" ht="13.2">
+      <c r="E322" s="22"/>
+      <c r="N322" s="22"/>
+    </row>
+    <row r="323" spans="5:14" ht="13.2">
+      <c r="E323" s="22"/>
+      <c r="N323" s="22"/>
+    </row>
+    <row r="324" spans="5:14" ht="13.2">
+      <c r="E324" s="22"/>
+      <c r="N324" s="22"/>
+    </row>
+    <row r="325" spans="5:14" ht="13.2">
+      <c r="E325" s="22"/>
+      <c r="N325" s="22"/>
+    </row>
+    <row r="326" spans="5:14" ht="13.2">
+      <c r="E326" s="22"/>
+      <c r="N326" s="22"/>
+    </row>
+    <row r="327" spans="5:14" ht="13.2">
+      <c r="E327" s="22"/>
+      <c r="N327" s="22"/>
+    </row>
+    <row r="328" spans="5:14" ht="13.2">
+      <c r="E328" s="22"/>
+      <c r="N328" s="22"/>
+    </row>
+    <row r="329" spans="5:14" ht="13.2">
+      <c r="E329" s="22"/>
+      <c r="N329" s="22"/>
+    </row>
+    <row r="330" spans="5:14" ht="13.2">
+      <c r="E330" s="22"/>
+      <c r="N330" s="22"/>
+    </row>
+    <row r="331" spans="5:14" ht="13.2">
+      <c r="E331" s="22"/>
+      <c r="N331" s="22"/>
+    </row>
+    <row r="332" spans="5:14" ht="13.2">
+      <c r="E332" s="22"/>
+      <c r="N332" s="22"/>
+    </row>
+    <row r="333" spans="5:14" ht="13.2">
+      <c r="E333" s="22"/>
+      <c r="N333" s="22"/>
+    </row>
+    <row r="334" spans="5:14" ht="13.2">
+      <c r="E334" s="22"/>
+      <c r="N334" s="22"/>
+    </row>
+    <row r="335" spans="5:14" ht="13.2">
+      <c r="E335" s="22"/>
+      <c r="N335" s="22"/>
+    </row>
+    <row r="336" spans="5:14" ht="13.2">
+      <c r="E336" s="22"/>
+      <c r="N336" s="22"/>
+    </row>
+    <row r="337" spans="5:14" ht="13.2">
+      <c r="E337" s="22"/>
+      <c r="N337" s="22"/>
+    </row>
+    <row r="338" spans="5:14" ht="13.2">
+      <c r="E338" s="22"/>
+      <c r="N338" s="22"/>
+    </row>
+    <row r="339" spans="5:14" ht="13.2">
+      <c r="E339" s="22"/>
+      <c r="N339" s="22"/>
+    </row>
+    <row r="340" spans="5:14" ht="13.2">
+      <c r="E340" s="22"/>
+      <c r="N340" s="22"/>
+    </row>
+    <row r="341" spans="5:14" ht="13.2">
+      <c r="E341" s="22"/>
+      <c r="N341" s="22"/>
+    </row>
+    <row r="342" spans="5:14" ht="13.2">
+      <c r="E342" s="22"/>
+      <c r="N342" s="22"/>
+    </row>
+    <row r="343" spans="5:14" ht="13.2">
+      <c r="E343" s="22"/>
+      <c r="N343" s="22"/>
+    </row>
+    <row r="344" spans="5:14" ht="13.2">
+      <c r="E344" s="22"/>
+      <c r="N344" s="22"/>
+    </row>
+    <row r="345" spans="5:14" ht="13.2">
+      <c r="E345" s="22"/>
+      <c r="N345" s="22"/>
+    </row>
+    <row r="346" spans="5:14" ht="13.2">
+      <c r="E346" s="22"/>
+      <c r="N346" s="22"/>
+    </row>
+    <row r="347" spans="5:14" ht="13.2">
+      <c r="E347" s="22"/>
+      <c r="N347" s="22"/>
+    </row>
+    <row r="348" spans="5:14" ht="13.2">
+      <c r="E348" s="22"/>
+      <c r="N348" s="22"/>
+    </row>
+    <row r="349" spans="5:14" ht="13.2">
+      <c r="E349" s="22"/>
+      <c r="N349" s="22"/>
+    </row>
+    <row r="350" spans="5:14" ht="13.2">
+      <c r="E350" s="22"/>
+      <c r="N350" s="22"/>
+    </row>
+    <row r="351" spans="5:14" ht="13.2">
+      <c r="E351" s="22"/>
+      <c r="N351" s="22"/>
+    </row>
+    <row r="352" spans="5:14" ht="13.2">
+      <c r="E352" s="22"/>
+      <c r="N352" s="22"/>
+    </row>
+    <row r="353" spans="5:14" ht="13.2">
+      <c r="E353" s="22"/>
+      <c r="N353" s="22"/>
+    </row>
+    <row r="354" spans="5:14" ht="13.2">
+      <c r="E354" s="22"/>
+      <c r="N354" s="22"/>
+    </row>
+    <row r="355" spans="5:14" ht="13.2">
+      <c r="E355" s="22"/>
+      <c r="N355" s="22"/>
+    </row>
+    <row r="356" spans="5:14" ht="13.2">
+      <c r="E356" s="22"/>
+      <c r="N356" s="22"/>
+    </row>
+    <row r="357" spans="5:14" ht="13.2">
+      <c r="E357" s="22"/>
+      <c r="N357" s="22"/>
+    </row>
+    <row r="358" spans="5:14" ht="13.2">
+      <c r="E358" s="22"/>
+      <c r="N358" s="22"/>
+    </row>
+    <row r="359" spans="5:14" ht="13.2">
+      <c r="E359" s="22"/>
+      <c r="N359" s="22"/>
+    </row>
+    <row r="360" spans="5:14" ht="13.2">
+      <c r="E360" s="22"/>
+      <c r="N360" s="22"/>
+    </row>
+    <row r="361" spans="5:14" ht="13.2">
+      <c r="E361" s="22"/>
+      <c r="N361" s="22"/>
+    </row>
+    <row r="362" spans="5:14" ht="13.2">
+      <c r="E362" s="22"/>
+      <c r="N362" s="22"/>
+    </row>
+    <row r="363" spans="5:14" ht="13.2">
+      <c r="E363" s="22"/>
+      <c r="N363" s="22"/>
+    </row>
+    <row r="364" spans="5:14" ht="13.2">
+      <c r="E364" s="22"/>
+      <c r="N364" s="22"/>
+    </row>
+    <row r="365" spans="5:14" ht="13.2">
+      <c r="E365" s="22"/>
+      <c r="N365" s="22"/>
+    </row>
+    <row r="366" spans="5:14" ht="13.2">
+      <c r="E366" s="22"/>
+      <c r="N366" s="22"/>
+    </row>
+    <row r="367" spans="5:14" ht="13.2">
+      <c r="E367" s="22"/>
+      <c r="N367" s="22"/>
+    </row>
+    <row r="368" spans="5:14" ht="13.2">
+      <c r="E368" s="22"/>
+      <c r="N368" s="22"/>
+    </row>
+    <row r="369" spans="5:14" ht="13.2">
+      <c r="E369" s="22"/>
+      <c r="N369" s="22"/>
+    </row>
+    <row r="370" spans="5:14" ht="13.2">
+      <c r="E370" s="22"/>
+      <c r="N370" s="22"/>
+    </row>
+    <row r="371" spans="5:14" ht="13.2">
+      <c r="E371" s="22"/>
+      <c r="N371" s="22"/>
+    </row>
+    <row r="372" spans="5:14" ht="13.2">
+      <c r="E372" s="22"/>
+      <c r="N372" s="22"/>
+    </row>
+    <row r="373" spans="5:14" ht="13.2">
+      <c r="E373" s="22"/>
+      <c r="N373" s="22"/>
+    </row>
+    <row r="374" spans="5:14" ht="13.2">
+      <c r="E374" s="22"/>
+      <c r="N374" s="22"/>
+    </row>
+    <row r="375" spans="5:14" ht="13.2">
+      <c r="E375" s="22"/>
+      <c r="N375" s="22"/>
+    </row>
+    <row r="376" spans="5:14" ht="13.2">
+      <c r="E376" s="22"/>
+      <c r="N376" s="22"/>
+    </row>
+    <row r="377" spans="5:14" ht="13.2">
+      <c r="E377" s="22"/>
+      <c r="N377" s="22"/>
+    </row>
+    <row r="378" spans="5:14" ht="13.2">
+      <c r="E378" s="22"/>
+      <c r="N378" s="22"/>
+    </row>
+    <row r="379" spans="5:14" ht="13.2">
+      <c r="E379" s="22"/>
+      <c r="N379" s="22"/>
+    </row>
+    <row r="380" spans="5:14" ht="13.2">
+      <c r="E380" s="22"/>
+      <c r="N380" s="22"/>
+    </row>
+    <row r="381" spans="5:14" ht="13.2">
+      <c r="E381" s="22"/>
+      <c r="N381" s="22"/>
+    </row>
+    <row r="382" spans="5:14" ht="13.2">
+      <c r="E382" s="22"/>
+      <c r="N382" s="22"/>
+    </row>
+    <row r="383" spans="5:14" ht="13.2">
+      <c r="E383" s="22"/>
+      <c r="N383" s="22"/>
+    </row>
+    <row r="384" spans="5:14" ht="13.2">
+      <c r="E384" s="22"/>
+      <c r="N384" s="22"/>
+    </row>
+    <row r="385" spans="5:14" ht="13.2">
+      <c r="E385" s="22"/>
+      <c r="N385" s="22"/>
+    </row>
+    <row r="386" spans="5:14" ht="13.2">
+      <c r="E386" s="22"/>
+      <c r="N386" s="22"/>
+    </row>
+    <row r="387" spans="5:14" ht="13.2">
+      <c r="E387" s="22"/>
+      <c r="N387" s="22"/>
+    </row>
+    <row r="388" spans="5:14" ht="13.2">
+      <c r="E388" s="22"/>
+      <c r="N388" s="22"/>
+    </row>
+    <row r="389" spans="5:14" ht="13.2">
+      <c r="E389" s="22"/>
+      <c r="N389" s="22"/>
+    </row>
+    <row r="390" spans="5:14" ht="13.2">
+      <c r="E390" s="22"/>
+      <c r="N390" s="22"/>
+    </row>
+    <row r="391" spans="5:14" ht="13.2">
+      <c r="E391" s="22"/>
+      <c r="N391" s="22"/>
+    </row>
+    <row r="392" spans="5:14" ht="13.2">
+      <c r="E392" s="22"/>
+      <c r="N392" s="22"/>
+    </row>
+    <row r="393" spans="5:14" ht="13.2">
+      <c r="E393" s="22"/>
+      <c r="N393" s="22"/>
+    </row>
+    <row r="394" spans="5:14" ht="13.2">
+      <c r="E394" s="22"/>
+      <c r="N394" s="22"/>
+    </row>
+    <row r="395" spans="5:14" ht="13.2">
+      <c r="E395" s="22"/>
+      <c r="N395" s="22"/>
+    </row>
+    <row r="396" spans="5:14" ht="13.2">
+      <c r="E396" s="22"/>
+      <c r="N396" s="22"/>
+    </row>
+    <row r="397" spans="5:14" ht="13.2">
+      <c r="E397" s="22"/>
+      <c r="N397" s="22"/>
+    </row>
+    <row r="398" spans="5:14" ht="13.2">
+      <c r="E398" s="22"/>
+      <c r="N398" s="22"/>
+    </row>
+    <row r="399" spans="5:14" ht="13.2">
+      <c r="E399" s="22"/>
+      <c r="N399" s="22"/>
+    </row>
+    <row r="400" spans="5:14" ht="13.2">
+      <c r="E400" s="22"/>
+      <c r="N400" s="22"/>
+    </row>
+    <row r="401" spans="5:14" ht="13.2">
+      <c r="E401" s="22"/>
+      <c r="N401" s="22"/>
+    </row>
+    <row r="402" spans="5:14" ht="13.2">
+      <c r="E402" s="22"/>
+      <c r="N402" s="22"/>
+    </row>
+    <row r="403" spans="5:14" ht="13.2">
+      <c r="E403" s="22"/>
+      <c r="N403" s="22"/>
+    </row>
+    <row r="404" spans="5:14" ht="13.2">
+      <c r="E404" s="22"/>
+      <c r="N404" s="22"/>
+    </row>
+    <row r="405" spans="5:14" ht="13.2">
+      <c r="E405" s="22"/>
+      <c r="N405" s="22"/>
+    </row>
+    <row r="406" spans="5:14" ht="13.2">
+      <c r="E406" s="22"/>
+      <c r="N406" s="22"/>
+    </row>
+    <row r="407" spans="5:14" ht="13.2">
+      <c r="E407" s="22"/>
+      <c r="N407" s="22"/>
+    </row>
+    <row r="408" spans="5:14" ht="13.2">
+      <c r="E408" s="22"/>
+      <c r="N408" s="22"/>
+    </row>
+    <row r="409" spans="5:14" ht="13.2">
+      <c r="E409" s="22"/>
+      <c r="N409" s="22"/>
+    </row>
+    <row r="410" spans="5:14" ht="13.2">
+      <c r="E410" s="22"/>
+      <c r="N410" s="22"/>
+    </row>
+    <row r="411" spans="5:14" ht="13.2">
+      <c r="E411" s="22"/>
+      <c r="N411" s="22"/>
+    </row>
+    <row r="412" spans="5:14" ht="13.2">
+      <c r="E412" s="22"/>
+      <c r="N412" s="22"/>
+    </row>
+    <row r="413" spans="5:14" ht="13.2">
+      <c r="E413" s="22"/>
+      <c r="N413" s="22"/>
+    </row>
+    <row r="414" spans="5:14" ht="13.2">
+      <c r="E414" s="22"/>
+      <c r="N414" s="22"/>
+    </row>
+    <row r="415" spans="5:14" ht="13.2">
+      <c r="E415" s="22"/>
+      <c r="N415" s="22"/>
+    </row>
+    <row r="416" spans="5:14" ht="13.2">
+      <c r="E416" s="22"/>
+      <c r="N416" s="22"/>
+    </row>
+    <row r="417" spans="5:14" ht="13.2">
+      <c r="E417" s="22"/>
+      <c r="N417" s="22"/>
+    </row>
+    <row r="418" spans="5:14" ht="13.2">
+      <c r="E418" s="22"/>
+      <c r="N418" s="22"/>
+    </row>
+    <row r="419" spans="5:14" ht="13.2">
+      <c r="E419" s="22"/>
+      <c r="N419" s="22"/>
+    </row>
+    <row r="420" spans="5:14" ht="13.2">
+      <c r="E420" s="22"/>
+      <c r="N420" s="22"/>
+    </row>
+    <row r="421" spans="5:14" ht="13.2">
+      <c r="E421" s="22"/>
+      <c r="N421" s="22"/>
+    </row>
+    <row r="422" spans="5:14" ht="13.2">
+      <c r="E422" s="22"/>
+      <c r="N422" s="22"/>
+    </row>
+    <row r="423" spans="5:14" ht="13.2">
+      <c r="E423" s="22"/>
+      <c r="N423" s="22"/>
+    </row>
+    <row r="424" spans="5:14" ht="13.2">
+      <c r="E424" s="22"/>
+      <c r="N424" s="22"/>
+    </row>
+    <row r="425" spans="5:14" ht="13.2">
+      <c r="E425" s="22"/>
+      <c r="N425" s="22"/>
+    </row>
+    <row r="426" spans="5:14" ht="13.2">
+      <c r="E426" s="22"/>
+      <c r="N426" s="22"/>
+    </row>
+    <row r="427" spans="5:14" ht="13.2">
+      <c r="E427" s="22"/>
+      <c r="N427" s="22"/>
+    </row>
+    <row r="428" spans="5:14" ht="13.2">
+      <c r="E428" s="22"/>
+      <c r="N428" s="22"/>
+    </row>
+    <row r="429" spans="5:14" ht="13.2">
+      <c r="E429" s="22"/>
+      <c r="N429" s="22"/>
+    </row>
+    <row r="430" spans="5:14" ht="13.2">
+      <c r="E430" s="22"/>
+      <c r="N430" s="22"/>
+    </row>
+    <row r="431" spans="5:14" ht="13.2">
+      <c r="E431" s="22"/>
+      <c r="N431" s="22"/>
+    </row>
+    <row r="432" spans="5:14" ht="13.2">
+      <c r="E432" s="22"/>
+      <c r="N432" s="22"/>
+    </row>
+    <row r="433" spans="5:14" ht="13.2">
+      <c r="E433" s="22"/>
+      <c r="N433" s="22"/>
+    </row>
+    <row r="434" spans="5:14" ht="13.2">
+      <c r="E434" s="22"/>
+      <c r="N434" s="22"/>
+    </row>
+    <row r="435" spans="5:14" ht="13.2">
+      <c r="E435" s="22"/>
+      <c r="N435" s="22"/>
+    </row>
+    <row r="436" spans="5:14" ht="13.2">
+      <c r="E436" s="22"/>
+      <c r="N436" s="22"/>
+    </row>
+    <row r="437" spans="5:14" ht="13.2">
+      <c r="E437" s="22"/>
+      <c r="N437" s="22"/>
+    </row>
+    <row r="438" spans="5:14" ht="13.2">
+      <c r="E438" s="22"/>
+      <c r="N438" s="22"/>
+    </row>
+    <row r="439" spans="5:14" ht="13.2">
+      <c r="E439" s="22"/>
+      <c r="N439" s="22"/>
+    </row>
+    <row r="440" spans="5:14" ht="13.2">
+      <c r="E440" s="22"/>
+      <c r="N440" s="22"/>
+    </row>
+    <row r="441" spans="5:14" ht="13.2">
+      <c r="E441" s="22"/>
+      <c r="N441" s="22"/>
+    </row>
+    <row r="442" spans="5:14" ht="13.2">
+      <c r="E442" s="22"/>
+      <c r="N442" s="22"/>
+    </row>
+    <row r="443" spans="5:14" ht="13.2">
+      <c r="E443" s="22"/>
+      <c r="N443" s="22"/>
+    </row>
+    <row r="444" spans="5:14" ht="13.2">
+      <c r="E444" s="22"/>
+      <c r="N444" s="22"/>
+    </row>
+    <row r="445" spans="5:14" ht="13.2">
+      <c r="E445" s="22"/>
+      <c r="N445" s="22"/>
+    </row>
+    <row r="446" spans="5:14" ht="13.2">
+      <c r="E446" s="22"/>
+      <c r="N446" s="22"/>
+    </row>
+    <row r="447" spans="5:14" ht="13.2">
+      <c r="E447" s="22"/>
+      <c r="N447" s="22"/>
+    </row>
+    <row r="448" spans="5:14" ht="13.2">
+      <c r="E448" s="22"/>
+      <c r="N448" s="22"/>
+    </row>
+    <row r="449" spans="5:14" ht="13.2">
+      <c r="E449" s="22"/>
+      <c r="N449" s="22"/>
+    </row>
+    <row r="450" spans="5:14" ht="13.2">
+      <c r="E450" s="22"/>
+      <c r="N450" s="22"/>
+    </row>
+    <row r="451" spans="5:14" ht="13.2">
+      <c r="E451" s="22"/>
+      <c r="N451" s="22"/>
+    </row>
+    <row r="452" spans="5:14" ht="13.2">
+      <c r="E452" s="22"/>
+      <c r="N452" s="22"/>
+    </row>
+    <row r="453" spans="5:14" ht="13.2">
+      <c r="E453" s="22"/>
+      <c r="N453" s="22"/>
+    </row>
+    <row r="454" spans="5:14" ht="13.2">
+      <c r="E454" s="22"/>
+      <c r="N454" s="22"/>
+    </row>
+    <row r="455" spans="5:14" ht="13.2">
+      <c r="E455" s="22"/>
+      <c r="N455" s="22"/>
+    </row>
+    <row r="456" spans="5:14" ht="13.2">
+      <c r="E456" s="22"/>
+      <c r="N456" s="22"/>
+    </row>
+    <row r="457" spans="5:14" ht="13.2">
+      <c r="E457" s="22"/>
+      <c r="N457" s="22"/>
+    </row>
+    <row r="458" spans="5:14" ht="13.2">
+      <c r="E458" s="22"/>
+      <c r="N458" s="22"/>
+    </row>
+    <row r="459" spans="5:14" ht="13.2">
+      <c r="E459" s="22"/>
+      <c r="N459" s="22"/>
+    </row>
+    <row r="460" spans="5:14" ht="13.2">
+      <c r="E460" s="22"/>
+      <c r="N460" s="22"/>
+    </row>
+    <row r="461" spans="5:14" ht="13.2">
+      <c r="E461" s="22"/>
+      <c r="N461" s="22"/>
+    </row>
+    <row r="462" spans="5:14" ht="13.2">
+      <c r="E462" s="22"/>
+      <c r="N462" s="22"/>
+    </row>
+    <row r="463" spans="5:14" ht="13.2">
+      <c r="E463" s="22"/>
+      <c r="N463" s="22"/>
+    </row>
+    <row r="464" spans="5:14" ht="13.2">
+      <c r="E464" s="22"/>
+      <c r="N464" s="22"/>
+    </row>
+    <row r="465" spans="5:14" ht="13.2">
+      <c r="E465" s="22"/>
+      <c r="N465" s="22"/>
+    </row>
+    <row r="466" spans="5:14" ht="13.2">
+      <c r="E466" s="22"/>
+      <c r="N466" s="22"/>
+    </row>
+    <row r="467" spans="5:14" ht="13.2">
+      <c r="E467" s="22"/>
+      <c r="N467" s="22"/>
+    </row>
+    <row r="468" spans="5:14" ht="13.2">
+      <c r="E468" s="22"/>
+      <c r="N468" s="22"/>
+    </row>
+    <row r="469" spans="5:14" ht="13.2">
+      <c r="E469" s="22"/>
+      <c r="N469" s="22"/>
+    </row>
+    <row r="470" spans="5:14" ht="13.2">
+      <c r="E470" s="22"/>
+      <c r="N470" s="22"/>
+    </row>
+    <row r="471" spans="5:14" ht="13.2">
+      <c r="E471" s="22"/>
+      <c r="N471" s="22"/>
+    </row>
+    <row r="472" spans="5:14" ht="13.2">
+      <c r="E472" s="22"/>
+      <c r="N472" s="22"/>
+    </row>
+    <row r="473" spans="5:14" ht="13.2">
+      <c r="E473" s="22"/>
+      <c r="N473" s="22"/>
+    </row>
+    <row r="474" spans="5:14" ht="13.2">
+      <c r="E474" s="22"/>
+      <c r="N474" s="22"/>
+    </row>
+    <row r="475" spans="5:14" ht="13.2">
+      <c r="E475" s="22"/>
+      <c r="N475" s="22"/>
+    </row>
+    <row r="476" spans="5:14" ht="13.2">
+      <c r="E476" s="22"/>
+      <c r="N476" s="22"/>
+    </row>
+    <row r="477" spans="5:14" ht="13.2">
+      <c r="E477" s="22"/>
+      <c r="N477" s="22"/>
+    </row>
+    <row r="478" spans="5:14" ht="13.2">
+      <c r="E478" s="22"/>
+      <c r="N478" s="22"/>
+    </row>
+    <row r="479" spans="5:14" ht="13.2">
+      <c r="E479" s="22"/>
+      <c r="N479" s="22"/>
+    </row>
+    <row r="480" spans="5:14" ht="13.2">
+      <c r="E480" s="22"/>
+      <c r="N480" s="22"/>
+    </row>
+    <row r="481" spans="5:14" ht="13.2">
+      <c r="E481" s="22"/>
+      <c r="N481" s="22"/>
+    </row>
+    <row r="482" spans="5:14" ht="13.2">
+      <c r="E482" s="22"/>
+      <c r="N482" s="22"/>
+    </row>
+    <row r="483" spans="5:14" ht="13.2">
+      <c r="E483" s="22"/>
+      <c r="N483" s="22"/>
+    </row>
+    <row r="484" spans="5:14" ht="13.2">
+      <c r="E484" s="22"/>
+      <c r="N484" s="22"/>
+    </row>
+    <row r="485" spans="5:14" ht="13.2">
+      <c r="E485" s="22"/>
+      <c r="N485" s="22"/>
+    </row>
+    <row r="486" spans="5:14" ht="13.2">
+      <c r="E486" s="22"/>
+      <c r="N486" s="22"/>
+    </row>
+    <row r="487" spans="5:14" ht="13.2">
+      <c r="E487" s="22"/>
+      <c r="N487" s="22"/>
+    </row>
+    <row r="488" spans="5:14" ht="13.2">
+      <c r="E488" s="22"/>
+      <c r="N488" s="22"/>
+    </row>
+    <row r="489" spans="5:14" ht="13.2">
+      <c r="E489" s="22"/>
+      <c r="N489" s="22"/>
+    </row>
+    <row r="490" spans="5:14" ht="13.2">
+      <c r="E490" s="22"/>
+      <c r="N490" s="22"/>
+    </row>
+    <row r="491" spans="5:14" ht="13.2">
+      <c r="E491" s="22"/>
+      <c r="N491" s="22"/>
+    </row>
+    <row r="492" spans="5:14" ht="13.2">
+      <c r="E492" s="22"/>
+      <c r="N492" s="22"/>
+    </row>
+    <row r="493" spans="5:14" ht="13.2">
+      <c r="E493" s="22"/>
+      <c r="N493" s="22"/>
+    </row>
+    <row r="494" spans="5:14" ht="13.2">
+      <c r="E494" s="22"/>
+      <c r="N494" s="22"/>
+    </row>
+    <row r="495" spans="5:14" ht="13.2">
+      <c r="E495" s="22"/>
+      <c r="N495" s="22"/>
+    </row>
+    <row r="496" spans="5:14" ht="13.2">
+      <c r="E496" s="22"/>
+      <c r="N496" s="22"/>
+    </row>
+    <row r="497" spans="5:14" ht="13.2">
+      <c r="E497" s="22"/>
+      <c r="N497" s="22"/>
+    </row>
+    <row r="498" spans="5:14" ht="13.2">
+      <c r="E498" s="22"/>
+      <c r="N498" s="22"/>
+    </row>
+    <row r="499" spans="5:14" ht="13.2">
+      <c r="E499" s="22"/>
+      <c r="N499" s="22"/>
+    </row>
+    <row r="500" spans="5:14" ht="13.2">
+      <c r="E500" s="22"/>
+      <c r="N500" s="22"/>
+    </row>
+    <row r="501" spans="5:14" ht="13.2">
+      <c r="E501" s="22"/>
+      <c r="N501" s="22"/>
+    </row>
+    <row r="502" spans="5:14" ht="13.2">
+      <c r="E502" s="22"/>
+      <c r="N502" s="22"/>
+    </row>
+    <row r="503" spans="5:14" ht="13.2">
+      <c r="E503" s="22"/>
+      <c r="N503" s="22"/>
+    </row>
+    <row r="504" spans="5:14" ht="13.2">
+      <c r="E504" s="22"/>
+      <c r="N504" s="22"/>
+    </row>
+    <row r="505" spans="5:14" ht="13.2">
+      <c r="E505" s="22"/>
+      <c r="N505" s="22"/>
+    </row>
+    <row r="506" spans="5:14" ht="13.2">
+      <c r="E506" s="22"/>
+      <c r="N506" s="22"/>
+    </row>
+    <row r="507" spans="5:14" ht="13.2">
+      <c r="E507" s="22"/>
+      <c r="N507" s="22"/>
+    </row>
+    <row r="508" spans="5:14" ht="13.2">
+      <c r="E508" s="22"/>
+      <c r="N508" s="22"/>
+    </row>
+    <row r="509" spans="5:14" ht="13.2">
+      <c r="E509" s="22"/>
+      <c r="N509" s="22"/>
+    </row>
+    <row r="510" spans="5:14" ht="13.2">
+      <c r="E510" s="22"/>
+      <c r="N510" s="22"/>
+    </row>
+    <row r="511" spans="5:14" ht="13.2">
+      <c r="E511" s="22"/>
+      <c r="N511" s="22"/>
+    </row>
+    <row r="512" spans="5:14" ht="13.2">
+      <c r="E512" s="22"/>
+      <c r="N512" s="22"/>
+    </row>
+    <row r="513" spans="5:14" ht="13.2">
+      <c r="E513" s="22"/>
+      <c r="N513" s="22"/>
+    </row>
+    <row r="514" spans="5:14" ht="13.2">
+      <c r="E514" s="22"/>
+      <c r="N514" s="22"/>
+    </row>
+    <row r="515" spans="5:14" ht="13.2">
+      <c r="E515" s="22"/>
+      <c r="N515" s="22"/>
+    </row>
+    <row r="516" spans="5:14" ht="13.2">
+      <c r="E516" s="22"/>
+      <c r="N516" s="22"/>
+    </row>
+    <row r="517" spans="5:14" ht="13.2">
+      <c r="E517" s="22"/>
+      <c r="N517" s="22"/>
+    </row>
+    <row r="518" spans="5:14" ht="13.2">
+      <c r="E518" s="22"/>
+      <c r="N518" s="22"/>
+    </row>
+    <row r="519" spans="5:14" ht="13.2">
+      <c r="E519" s="22"/>
+      <c r="N519" s="22"/>
+    </row>
+    <row r="520" spans="5:14" ht="13.2">
+      <c r="E520" s="22"/>
+      <c r="N520" s="22"/>
+    </row>
+    <row r="521" spans="5:14" ht="13.2">
+      <c r="E521" s="22"/>
+      <c r="N521" s="22"/>
+    </row>
+    <row r="522" spans="5:14" ht="13.2">
+      <c r="E522" s="22"/>
+      <c r="N522" s="22"/>
+    </row>
+    <row r="523" spans="5:14" ht="13.2">
+      <c r="E523" s="22"/>
+      <c r="N523" s="22"/>
+    </row>
+    <row r="524" spans="5:14" ht="13.2">
+      <c r="E524" s="22"/>
+      <c r="N524" s="22"/>
+    </row>
+    <row r="525" spans="5:14" ht="13.2">
+      <c r="E525" s="22"/>
+      <c r="N525" s="22"/>
+    </row>
+    <row r="526" spans="5:14" ht="13.2">
+      <c r="E526" s="22"/>
+      <c r="N526" s="22"/>
+    </row>
+    <row r="527" spans="5:14" ht="13.2">
+      <c r="E527" s="22"/>
+      <c r="N527" s="22"/>
+    </row>
+    <row r="528" spans="5:14" ht="13.2">
+      <c r="E528" s="22"/>
+      <c r="N528" s="22"/>
+    </row>
+    <row r="529" spans="5:14" ht="13.2">
+      <c r="E529" s="22"/>
+      <c r="N529" s="22"/>
+    </row>
+    <row r="530" spans="5:14" ht="13.2">
+      <c r="E530" s="22"/>
+      <c r="N530" s="22"/>
+    </row>
+    <row r="531" spans="5:14" ht="13.2">
+      <c r="E531" s="22"/>
+      <c r="N531" s="22"/>
+    </row>
+    <row r="532" spans="5:14" ht="13.2">
+      <c r="E532" s="22"/>
+      <c r="N532" s="22"/>
+    </row>
+    <row r="533" spans="5:14" ht="13.2">
+      <c r="E533" s="22"/>
+      <c r="N533" s="22"/>
+    </row>
+    <row r="534" spans="5:14" ht="13.2">
+      <c r="E534" s="22"/>
+      <c r="N534" s="22"/>
+    </row>
+    <row r="535" spans="5:14" ht="13.2">
+      <c r="E535" s="22"/>
+      <c r="N535" s="22"/>
+    </row>
+    <row r="536" spans="5:14" ht="13.2">
+      <c r="E536" s="22"/>
+      <c r="N536" s="22"/>
+    </row>
+    <row r="537" spans="5:14" ht="13.2">
+      <c r="E537" s="22"/>
+      <c r="N537" s="22"/>
+    </row>
+    <row r="538" spans="5:14" ht="13.2">
+      <c r="E538" s="22"/>
+      <c r="N538" s="22"/>
+    </row>
+    <row r="539" spans="5:14" ht="13.2">
+      <c r="E539" s="22"/>
+      <c r="N539" s="22"/>
+    </row>
+    <row r="540" spans="5:14" ht="13.2">
+      <c r="E540" s="22"/>
+      <c r="N540" s="22"/>
+    </row>
+    <row r="541" spans="5:14" ht="13.2">
+      <c r="E541" s="22"/>
+      <c r="N541" s="22"/>
+    </row>
+    <row r="542" spans="5:14" ht="13.2">
+      <c r="E542" s="22"/>
+      <c r="N542" s="22"/>
+    </row>
+    <row r="543" spans="5:14" ht="13.2">
+      <c r="E543" s="22"/>
+      <c r="N543" s="22"/>
+    </row>
+    <row r="544" spans="5:14" ht="13.2">
+      <c r="E544" s="22"/>
+      <c r="N544" s="22"/>
+    </row>
+    <row r="545" spans="5:14" ht="13.2">
+      <c r="E545" s="22"/>
+      <c r="N545" s="22"/>
+    </row>
+    <row r="546" spans="5:14" ht="13.2">
+      <c r="E546" s="22"/>
+      <c r="N546" s="22"/>
+    </row>
+    <row r="547" spans="5:14" ht="13.2">
+      <c r="E547" s="22"/>
+      <c r="N547" s="22"/>
+    </row>
+    <row r="548" spans="5:14" ht="13.2">
+      <c r="E548" s="22"/>
+      <c r="N548" s="22"/>
+    </row>
+    <row r="549" spans="5:14" ht="13.2">
+      <c r="E549" s="22"/>
+      <c r="N549" s="22"/>
+    </row>
+    <row r="550" spans="5:14" ht="13.2">
+      <c r="E550" s="22"/>
+      <c r="N550" s="22"/>
+    </row>
+    <row r="551" spans="5:14" ht="13.2">
+      <c r="E551" s="22"/>
+      <c r="N551" s="22"/>
+    </row>
+    <row r="552" spans="5:14" ht="13.2">
+      <c r="E552" s="22"/>
+      <c r="N552" s="22"/>
+    </row>
+    <row r="553" spans="5:14" ht="13.2">
+      <c r="E553" s="22"/>
+      <c r="N553" s="22"/>
+    </row>
+    <row r="554" spans="5:14" ht="13.2">
+      <c r="E554" s="22"/>
+      <c r="N554" s="22"/>
+    </row>
+    <row r="555" spans="5:14" ht="13.2">
+      <c r="E555" s="22"/>
+      <c r="N555" s="22"/>
+    </row>
+    <row r="556" spans="5:14" ht="13.2">
+      <c r="E556" s="22"/>
+      <c r="N556" s="22"/>
+    </row>
+    <row r="557" spans="5:14" ht="13.2">
+      <c r="E557" s="22"/>
+      <c r="N557" s="22"/>
+    </row>
+    <row r="558" spans="5:14" ht="13.2">
+      <c r="E558" s="22"/>
+      <c r="N558" s="22"/>
+    </row>
+    <row r="559" spans="5:14" ht="13.2">
+      <c r="E559" s="22"/>
+      <c r="N559" s="22"/>
+    </row>
+    <row r="560" spans="5:14" ht="13.2">
+      <c r="E560" s="22"/>
+      <c r="N560" s="22"/>
+    </row>
+    <row r="561" spans="5:14" ht="13.2">
+      <c r="E561" s="22"/>
+      <c r="N561" s="22"/>
+    </row>
+    <row r="562" spans="5:14" ht="13.2">
+      <c r="E562" s="22"/>
+      <c r="N562" s="22"/>
+    </row>
+    <row r="563" spans="5:14" ht="13.2">
+      <c r="E563" s="22"/>
+      <c r="N563" s="22"/>
+    </row>
+    <row r="564" spans="5:14" ht="13.2">
+      <c r="E564" s="22"/>
+      <c r="N564" s="22"/>
+    </row>
+    <row r="565" spans="5:14" ht="13.2">
+      <c r="E565" s="22"/>
+      <c r="N565" s="22"/>
+    </row>
+    <row r="566" spans="5:14" ht="13.2">
+      <c r="E566" s="22"/>
+      <c r="N566" s="22"/>
+    </row>
+    <row r="567" spans="5:14" ht="13.2">
+      <c r="E567" s="22"/>
+      <c r="N567" s="22"/>
+    </row>
+    <row r="568" spans="5:14" ht="13.2">
+      <c r="E568" s="22"/>
+      <c r="N568" s="22"/>
+    </row>
+    <row r="569" spans="5:14" ht="13.2">
+      <c r="E569" s="22"/>
+      <c r="N569" s="22"/>
+    </row>
+    <row r="570" spans="5:14" ht="13.2">
+      <c r="E570" s="22"/>
+      <c r="N570" s="22"/>
+    </row>
+    <row r="571" spans="5:14" ht="13.2">
+      <c r="E571" s="22"/>
+      <c r="N571" s="22"/>
+    </row>
+    <row r="572" spans="5:14" ht="13.2">
+      <c r="E572" s="22"/>
+      <c r="N572" s="22"/>
+    </row>
+    <row r="573" spans="5:14" ht="13.2">
+      <c r="E573" s="22"/>
+      <c r="N573" s="22"/>
+    </row>
+    <row r="574" spans="5:14" ht="13.2">
+      <c r="E574" s="22"/>
+      <c r="N574" s="22"/>
+    </row>
+    <row r="575" spans="5:14" ht="13.2">
+      <c r="E575" s="22"/>
+      <c r="N575" s="22"/>
+    </row>
+    <row r="576" spans="5:14" ht="13.2">
+      <c r="E576" s="22"/>
+      <c r="N576" s="22"/>
+    </row>
+    <row r="577" spans="5:14" ht="13.2">
+      <c r="E577" s="22"/>
+      <c r="N577" s="22"/>
+    </row>
+    <row r="578" spans="5:14" ht="13.2">
+      <c r="E578" s="22"/>
+      <c r="N578" s="22"/>
+    </row>
+    <row r="579" spans="5:14" ht="13.2">
+      <c r="E579" s="22"/>
+      <c r="N579" s="22"/>
+    </row>
+    <row r="580" spans="5:14" ht="13.2">
+      <c r="E580" s="22"/>
+      <c r="N580" s="22"/>
+    </row>
+    <row r="581" spans="5:14" ht="13.2">
+      <c r="E581" s="22"/>
+      <c r="N581" s="22"/>
+    </row>
+    <row r="582" spans="5:14" ht="13.2">
+      <c r="E582" s="22"/>
+      <c r="N582" s="22"/>
+    </row>
+    <row r="583" spans="5:14" ht="13.2">
+      <c r="E583" s="22"/>
+      <c r="N583" s="22"/>
+    </row>
+    <row r="584" spans="5:14" ht="13.2">
+      <c r="E584" s="22"/>
+      <c r="N584" s="22"/>
+    </row>
+    <row r="585" spans="5:14" ht="13.2">
+      <c r="E585" s="22"/>
+      <c r="N585" s="22"/>
+    </row>
+    <row r="586" spans="5:14" ht="13.2">
+      <c r="E586" s="22"/>
+      <c r="N586" s="22"/>
+    </row>
+    <row r="587" spans="5:14" ht="13.2">
+      <c r="E587" s="22"/>
+      <c r="N587" s="22"/>
+    </row>
+    <row r="588" spans="5:14" ht="13.2">
+      <c r="E588" s="22"/>
+      <c r="N588" s="22"/>
+    </row>
+    <row r="589" spans="5:14" ht="13.2">
+      <c r="E589" s="22"/>
+      <c r="N589" s="22"/>
+    </row>
+    <row r="590" spans="5:14" ht="13.2">
+      <c r="E590" s="22"/>
+      <c r="N590" s="22"/>
+    </row>
+    <row r="591" spans="5:14" ht="13.2">
+      <c r="E591" s="22"/>
+      <c r="N591" s="22"/>
+    </row>
+    <row r="592" spans="5:14" ht="13.2">
+      <c r="E592" s="22"/>
+      <c r="N592" s="22"/>
+    </row>
+    <row r="593" spans="5:14" ht="13.2">
+      <c r="E593" s="22"/>
+      <c r="N593" s="22"/>
+    </row>
+    <row r="594" spans="5:14" ht="13.2">
+      <c r="E594" s="22"/>
+      <c r="N594" s="22"/>
+    </row>
+    <row r="595" spans="5:14" ht="13.2">
+      <c r="E595" s="22"/>
+      <c r="N595" s="22"/>
+    </row>
+    <row r="596" spans="5:14" ht="13.2">
+      <c r="E596" s="22"/>
+      <c r="N596" s="22"/>
+    </row>
+    <row r="597" spans="5:14" ht="13.2">
+      <c r="E597" s="22"/>
+      <c r="N597" s="22"/>
+    </row>
+    <row r="598" spans="5:14" ht="13.2">
+      <c r="E598" s="22"/>
+      <c r="N598" s="22"/>
+    </row>
+    <row r="599" spans="5:14" ht="13.2">
+      <c r="E599" s="22"/>
+      <c r="N599" s="22"/>
+    </row>
+    <row r="600" spans="5:14" ht="13.2">
+      <c r="E600" s="22"/>
+      <c r="N600" s="22"/>
+    </row>
+    <row r="601" spans="5:14" ht="13.2">
+      <c r="E601" s="22"/>
+      <c r="N601" s="22"/>
+    </row>
+    <row r="602" spans="5:14" ht="13.2">
+      <c r="E602" s="22"/>
+      <c r="N602" s="22"/>
+    </row>
+    <row r="603" spans="5:14" ht="13.2">
+      <c r="E603" s="22"/>
+      <c r="N603" s="22"/>
+    </row>
+    <row r="604" spans="5:14" ht="13.2">
+      <c r="E604" s="22"/>
+      <c r="N604" s="22"/>
+    </row>
+    <row r="605" spans="5:14" ht="13.2">
+      <c r="E605" s="22"/>
+      <c r="N605" s="22"/>
+    </row>
+    <row r="606" spans="5:14" ht="13.2">
+      <c r="E606" s="22"/>
+      <c r="N606" s="22"/>
+    </row>
+    <row r="607" spans="5:14" ht="13.2">
+      <c r="E607" s="22"/>
+      <c r="N607" s="22"/>
+    </row>
+    <row r="608" spans="5:14" ht="13.2">
+      <c r="E608" s="22"/>
+      <c r="N608" s="22"/>
+    </row>
+    <row r="609" spans="5:14" ht="13.2">
+      <c r="E609" s="22"/>
+      <c r="N609" s="22"/>
+    </row>
+    <row r="610" spans="5:14" ht="13.2">
+      <c r="E610" s="22"/>
+      <c r="N610" s="22"/>
+    </row>
+    <row r="611" spans="5:14" ht="13.2">
+      <c r="E611" s="22"/>
+      <c r="N611" s="22"/>
+    </row>
+    <row r="612" spans="5:14" ht="13.2">
+      <c r="E612" s="22"/>
+      <c r="N612" s="22"/>
+    </row>
+    <row r="613" spans="5:14" ht="13.2">
+      <c r="E613" s="22"/>
+      <c r="N613" s="22"/>
+    </row>
+    <row r="614" spans="5:14" ht="13.2">
+      <c r="E614" s="22"/>
+      <c r="N614" s="22"/>
+    </row>
+    <row r="615" spans="5:14" ht="13.2">
+      <c r="E615" s="22"/>
+      <c r="N615" s="22"/>
+    </row>
+    <row r="616" spans="5:14" ht="13.2">
+      <c r="E616" s="22"/>
+      <c r="N616" s="22"/>
+    </row>
+    <row r="617" spans="5:14" ht="13.2">
+      <c r="E617" s="22"/>
+      <c r="N617" s="22"/>
+    </row>
+    <row r="618" spans="5:14" ht="13.2">
+      <c r="E618" s="22"/>
+      <c r="N618" s="22"/>
+    </row>
+    <row r="619" spans="5:14" ht="13.2">
+      <c r="E619" s="22"/>
+      <c r="N619" s="22"/>
+    </row>
+    <row r="620" spans="5:14" ht="13.2">
+      <c r="E620" s="22"/>
+      <c r="N620" s="22"/>
+    </row>
+    <row r="621" spans="5:14" ht="13.2">
+      <c r="E621" s="22"/>
+      <c r="N621" s="22"/>
+    </row>
+    <row r="622" spans="5:14" ht="13.2">
+      <c r="E622" s="22"/>
+      <c r="N622" s="22"/>
+    </row>
+    <row r="623" spans="5:14" ht="13.2">
+      <c r="E623" s="22"/>
+      <c r="N623" s="22"/>
+    </row>
+    <row r="624" spans="5:14" ht="13.2">
+      <c r="E624" s="22"/>
+      <c r="N624" s="22"/>
+    </row>
+    <row r="625" spans="5:14" ht="13.2">
+      <c r="E625" s="22"/>
+      <c r="N625" s="22"/>
+    </row>
+    <row r="626" spans="5:14" ht="13.2">
+      <c r="E626" s="22"/>
+      <c r="N626" s="22"/>
+    </row>
+    <row r="627" spans="5:14" ht="13.2">
+      <c r="E627" s="22"/>
+      <c r="N627" s="22"/>
+    </row>
+    <row r="628" spans="5:14" ht="13.2">
+      <c r="E628" s="22"/>
+      <c r="N628" s="22"/>
+    </row>
+    <row r="629" spans="5:14" ht="13.2">
+      <c r="E629" s="22"/>
+      <c r="N629" s="22"/>
+    </row>
+    <row r="630" spans="5:14" ht="13.2">
+      <c r="E630" s="22"/>
+      <c r="N630" s="22"/>
+    </row>
+    <row r="631" spans="5:14" ht="13.2">
+      <c r="E631" s="22"/>
+      <c r="N631" s="22"/>
+    </row>
+    <row r="632" spans="5:14" ht="13.2">
+      <c r="E632" s="22"/>
+      <c r="N632" s="22"/>
+    </row>
+    <row r="633" spans="5:14" ht="13.2">
+      <c r="E633" s="22"/>
+      <c r="N633" s="22"/>
+    </row>
+    <row r="634" spans="5:14" ht="13.2">
+      <c r="E634" s="22"/>
+      <c r="N634" s="22"/>
+    </row>
+    <row r="635" spans="5:14" ht="13.2">
+      <c r="E635" s="22"/>
+      <c r="N635" s="22"/>
+    </row>
+    <row r="636" spans="5:14" ht="13.2">
+      <c r="E636" s="22"/>
+      <c r="N636" s="22"/>
+    </row>
+    <row r="637" spans="5:14" ht="13.2">
+      <c r="E637" s="22"/>
+      <c r="N637" s="22"/>
+    </row>
+    <row r="638" spans="5:14" ht="13.2">
+      <c r="E638" s="22"/>
+      <c r="N638" s="22"/>
+    </row>
+    <row r="639" spans="5:14" ht="13.2">
+      <c r="E639" s="22"/>
+      <c r="N639" s="22"/>
+    </row>
+    <row r="640" spans="5:14" ht="13.2">
+      <c r="E640" s="22"/>
+      <c r="N640" s="22"/>
+    </row>
+    <row r="641" spans="5:14" ht="13.2">
+      <c r="E641" s="22"/>
+      <c r="N641" s="22"/>
+    </row>
+    <row r="642" spans="5:14" ht="13.2">
+      <c r="E642" s="22"/>
+      <c r="N642" s="22"/>
+    </row>
+    <row r="643" spans="5:14" ht="13.2">
+      <c r="E643" s="22"/>
+      <c r="N643" s="22"/>
+    </row>
+    <row r="644" spans="5:14" ht="13.2">
+      <c r="E644" s="22"/>
+      <c r="N644" s="22"/>
+    </row>
+    <row r="645" spans="5:14" ht="13.2">
+      <c r="E645" s="22"/>
+      <c r="N645" s="22"/>
+    </row>
+    <row r="646" spans="5:14" ht="13.2">
+      <c r="E646" s="22"/>
+      <c r="N646" s="22"/>
+    </row>
+    <row r="647" spans="5:14" ht="13.2">
+      <c r="E647" s="22"/>
+      <c r="N647" s="22"/>
+    </row>
+    <row r="648" spans="5:14" ht="13.2">
+      <c r="E648" s="22"/>
+      <c r="N648" s="22"/>
+    </row>
+    <row r="649" spans="5:14" ht="13.2">
+      <c r="E649" s="22"/>
+      <c r="N649" s="22"/>
+    </row>
+    <row r="650" spans="5:14" ht="13.2">
+      <c r="E650" s="22"/>
+      <c r="N650" s="22"/>
+    </row>
+    <row r="651" spans="5:14" ht="13.2">
+      <c r="E651" s="22"/>
+      <c r="N651" s="22"/>
+    </row>
+    <row r="652" spans="5:14" ht="13.2">
+      <c r="E652" s="22"/>
+      <c r="N652" s="22"/>
+    </row>
+    <row r="653" spans="5:14" ht="13.2">
+      <c r="E653" s="22"/>
+      <c r="N653" s="22"/>
+    </row>
+    <row r="654" spans="5:14" ht="13.2">
+      <c r="E654" s="22"/>
+      <c r="N654" s="22"/>
+    </row>
+    <row r="655" spans="5:14" ht="13.2">
+      <c r="E655" s="22"/>
+      <c r="N655" s="22"/>
+    </row>
+    <row r="656" spans="5:14" ht="13.2">
+      <c r="E656" s="22"/>
+      <c r="N656" s="22"/>
+    </row>
+    <row r="657" spans="5:14" ht="13.2">
+      <c r="E657" s="22"/>
+      <c r="N657" s="22"/>
+    </row>
+    <row r="658" spans="5:14" ht="13.2">
+      <c r="E658" s="22"/>
+      <c r="N658" s="22"/>
+    </row>
+    <row r="659" spans="5:14" ht="13.2">
+      <c r="E659" s="22"/>
+      <c r="N659" s="22"/>
+    </row>
+    <row r="660" spans="5:14" ht="13.2">
+      <c r="E660" s="22"/>
+      <c r="N660" s="22"/>
+    </row>
+    <row r="661" spans="5:14" ht="13.2">
+      <c r="E661" s="22"/>
+      <c r="N661" s="22"/>
+    </row>
+    <row r="662" spans="5:14" ht="13.2">
+      <c r="E662" s="22"/>
+      <c r="N662" s="22"/>
+    </row>
+    <row r="663" spans="5:14" ht="13.2">
+      <c r="E663" s="22"/>
+      <c r="N663" s="22"/>
+    </row>
+    <row r="664" spans="5:14" ht="13.2">
+      <c r="E664" s="22"/>
+      <c r="N664" s="22"/>
+    </row>
+    <row r="665" spans="5:14" ht="13.2">
+      <c r="E665" s="22"/>
+      <c r="N665" s="22"/>
+    </row>
+    <row r="666" spans="5:14" ht="13.2">
+      <c r="E666" s="22"/>
+      <c r="N666" s="22"/>
+    </row>
+    <row r="667" spans="5:14" ht="13.2">
+      <c r="E667" s="22"/>
+      <c r="N667" s="22"/>
+    </row>
+    <row r="668" spans="5:14" ht="13.2">
+      <c r="E668" s="22"/>
+      <c r="N668" s="22"/>
+    </row>
+    <row r="669" spans="5:14" ht="13.2">
+      <c r="E669" s="22"/>
+      <c r="N669" s="22"/>
+    </row>
+    <row r="670" spans="5:14" ht="13.2">
+      <c r="E670" s="22"/>
+      <c r="N670" s="22"/>
+    </row>
+    <row r="671" spans="5:14" ht="13.2">
+      <c r="E671" s="22"/>
+      <c r="N671" s="22"/>
+    </row>
+    <row r="672" spans="5:14" ht="13.2">
+      <c r="E672" s="22"/>
+      <c r="N672" s="22"/>
+    </row>
+    <row r="673" spans="5:14" ht="13.2">
+      <c r="E673" s="22"/>
+      <c r="N673" s="22"/>
+    </row>
+    <row r="674" spans="5:14" ht="13.2">
+      <c r="E674" s="22"/>
+      <c r="N674" s="22"/>
+    </row>
+    <row r="675" spans="5:14" ht="13.2">
+      <c r="E675" s="22"/>
+      <c r="N675" s="22"/>
+    </row>
+    <row r="676" spans="5:14" ht="13.2">
+      <c r="E676" s="22"/>
+      <c r="N676" s="22"/>
+    </row>
+    <row r="677" spans="5:14" ht="13.2">
+      <c r="E677" s="22"/>
+      <c r="N677" s="22"/>
+    </row>
+    <row r="678" spans="5:14" ht="13.2">
+      <c r="E678" s="22"/>
+      <c r="N678" s="22"/>
+    </row>
+    <row r="679" spans="5:14" ht="13.2">
+      <c r="E679" s="22"/>
+      <c r="N679" s="22"/>
+    </row>
+    <row r="680" spans="5:14" ht="13.2">
+      <c r="E680" s="22"/>
+      <c r="N680" s="22"/>
+    </row>
+    <row r="681" spans="5:14" ht="13.2">
+      <c r="E681" s="22"/>
+      <c r="N681" s="22"/>
+    </row>
+    <row r="682" spans="5:14" ht="13.2">
+      <c r="E682" s="22"/>
+      <c r="N682" s="22"/>
+    </row>
+    <row r="683" spans="5:14" ht="13.2">
+      <c r="E683" s="22"/>
+      <c r="N683" s="22"/>
+    </row>
+    <row r="684" spans="5:14" ht="13.2">
+      <c r="E684" s="22"/>
+      <c r="N684" s="22"/>
+    </row>
+    <row r="685" spans="5:14" ht="13.2">
+      <c r="E685" s="22"/>
+      <c r="N685" s="22"/>
+    </row>
+    <row r="686" spans="5:14" ht="13.2">
+      <c r="E686" s="22"/>
+      <c r="N686" s="22"/>
+    </row>
+    <row r="687" spans="5:14" ht="13.2">
+      <c r="E687" s="22"/>
+      <c r="N687" s="22"/>
+    </row>
+    <row r="688" spans="5:14" ht="13.2">
+      <c r="E688" s="22"/>
+      <c r="N688" s="22"/>
+    </row>
+    <row r="689" spans="5:14" ht="13.2">
+      <c r="E689" s="22"/>
+      <c r="N689" s="22"/>
+    </row>
+    <row r="690" spans="5:14" ht="13.2">
+      <c r="E690" s="22"/>
+      <c r="N690" s="22"/>
+    </row>
+    <row r="691" spans="5:14" ht="13.2">
+      <c r="E691" s="22"/>
+      <c r="N691" s="22"/>
+    </row>
+    <row r="692" spans="5:14" ht="13.2">
+      <c r="E692" s="22"/>
+      <c r="N692" s="22"/>
+    </row>
+    <row r="693" spans="5:14" ht="13.2">
+      <c r="E693" s="22"/>
+      <c r="N693" s="22"/>
+    </row>
+    <row r="694" spans="5:14" ht="13.2">
+      <c r="E694" s="22"/>
+      <c r="N694" s="22"/>
+    </row>
+    <row r="695" spans="5:14" ht="13.2">
+      <c r="E695" s="22"/>
+      <c r="N695" s="22"/>
+    </row>
+    <row r="696" spans="5:14" ht="13.2">
+      <c r="E696" s="22"/>
+      <c r="N696" s="22"/>
+    </row>
+    <row r="697" spans="5:14" ht="13.2">
+      <c r="E697" s="22"/>
+      <c r="N697" s="22"/>
+    </row>
+    <row r="698" spans="5:14" ht="13.2">
+      <c r="E698" s="22"/>
+      <c r="N698" s="22"/>
+    </row>
+    <row r="699" spans="5:14" ht="13.2">
+      <c r="E699" s="22"/>
+      <c r="N699" s="22"/>
+    </row>
+    <row r="700" spans="5:14" ht="13.2">
+      <c r="E700" s="22"/>
+      <c r="N700" s="22"/>
+    </row>
+    <row r="701" spans="5:14" ht="13.2">
+      <c r="E701" s="22"/>
+      <c r="N701" s="22"/>
+    </row>
+    <row r="702" spans="5:14" ht="13.2">
+      <c r="E702" s="22"/>
+      <c r="N702" s="22"/>
+    </row>
+    <row r="703" spans="5:14" ht="13.2">
+      <c r="E703" s="22"/>
+      <c r="N703" s="22"/>
+    </row>
+    <row r="704" spans="5:14" ht="13.2">
+      <c r="E704" s="22"/>
+      <c r="N704" s="22"/>
+    </row>
+    <row r="705" spans="5:14" ht="13.2">
+      <c r="E705" s="22"/>
+      <c r="N705" s="22"/>
+    </row>
+    <row r="706" spans="5:14" ht="13.2">
+      <c r="E706" s="22"/>
+      <c r="N706" s="22"/>
+    </row>
+    <row r="707" spans="5:14" ht="13.2">
+      <c r="E707" s="22"/>
+      <c r="N707" s="22"/>
+    </row>
+    <row r="708" spans="5:14" ht="13.2">
+      <c r="E708" s="22"/>
+      <c r="N708" s="22"/>
+    </row>
+    <row r="709" spans="5:14" ht="13.2">
+      <c r="E709" s="22"/>
+      <c r="N709" s="22"/>
+    </row>
+    <row r="710" spans="5:14" ht="13.2">
+      <c r="E710" s="22"/>
+      <c r="N710" s="22"/>
+    </row>
+    <row r="711" spans="5:14" ht="13.2">
+      <c r="E711" s="22"/>
+      <c r="N711" s="22"/>
+    </row>
+    <row r="712" spans="5:14" ht="13.2">
+      <c r="E712" s="22"/>
+      <c r="N712" s="22"/>
+    </row>
+    <row r="713" spans="5:14" ht="13.2">
+      <c r="E713" s="22"/>
+      <c r="N713" s="22"/>
+    </row>
+    <row r="714" spans="5:14" ht="13.2">
+      <c r="E714" s="22"/>
+      <c r="N714" s="22"/>
+    </row>
+    <row r="715" spans="5:14" ht="13.2">
+      <c r="E715" s="22"/>
+      <c r="N715" s="22"/>
+    </row>
+    <row r="716" spans="5:14" ht="13.2">
+      <c r="E716" s="22"/>
+      <c r="N716" s="22"/>
+    </row>
+    <row r="717" spans="5:14" ht="13.2">
+      <c r="E717" s="22"/>
+      <c r="N717" s="22"/>
+    </row>
+    <row r="718" spans="5:14" ht="13.2">
+      <c r="E718" s="22"/>
+      <c r="N718" s="22"/>
+    </row>
+    <row r="719" spans="5:14" ht="13.2">
+      <c r="E719" s="22"/>
+      <c r="N719" s="22"/>
+    </row>
+    <row r="720" spans="5:14" ht="13.2">
+      <c r="E720" s="22"/>
+      <c r="N720" s="22"/>
+    </row>
+    <row r="721" spans="5:14" ht="13.2">
+      <c r="E721" s="22"/>
+      <c r="N721" s="22"/>
+    </row>
+    <row r="722" spans="5:14" ht="13.2">
+      <c r="E722" s="22"/>
+      <c r="N722" s="22"/>
+    </row>
+    <row r="723" spans="5:14" ht="13.2">
+      <c r="E723" s="22"/>
+      <c r="N723" s="22"/>
+    </row>
+    <row r="724" spans="5:14" ht="13.2">
+      <c r="E724" s="22"/>
+      <c r="N724" s="22"/>
+    </row>
+    <row r="725" spans="5:14" ht="13.2">
+      <c r="E725" s="22"/>
+      <c r="N725" s="22"/>
+    </row>
+    <row r="726" spans="5:14" ht="13.2">
+      <c r="E726" s="22"/>
+      <c r="N726" s="22"/>
+    </row>
+    <row r="727" spans="5:14" ht="13.2">
+      <c r="E727" s="22"/>
+      <c r="N727" s="22"/>
+    </row>
+    <row r="728" spans="5:14" ht="13.2">
+      <c r="E728" s="22"/>
+      <c r="N728" s="22"/>
+    </row>
+    <row r="729" spans="5:14" ht="13.2">
+      <c r="E729" s="22"/>
+      <c r="N729" s="22"/>
+    </row>
+    <row r="730" spans="5:14" ht="13.2">
+      <c r="E730" s="22"/>
+      <c r="N730" s="22"/>
+    </row>
+    <row r="731" spans="5:14" ht="13.2">
+      <c r="E731" s="22"/>
+      <c r="N731" s="22"/>
+    </row>
+    <row r="732" spans="5:14" ht="13.2">
+      <c r="E732" s="22"/>
+      <c r="N732" s="22"/>
+    </row>
+    <row r="733" spans="5:14" ht="13.2">
+      <c r="E733" s="22"/>
+      <c r="N733" s="22"/>
+    </row>
+    <row r="734" spans="5:14" ht="13.2">
+      <c r="E734" s="22"/>
+      <c r="N734" s="22"/>
+    </row>
+    <row r="735" spans="5:14" ht="13.2">
+      <c r="E735" s="22"/>
+      <c r="N735" s="22"/>
+    </row>
+    <row r="736" spans="5:14" ht="13.2">
+      <c r="E736" s="22"/>
+      <c r="N736" s="22"/>
+    </row>
+    <row r="737" spans="5:14" ht="13.2">
+      <c r="E737" s="22"/>
+      <c r="N737" s="22"/>
+    </row>
+    <row r="738" spans="5:14" ht="13.2">
+      <c r="E738" s="22"/>
+      <c r="N738" s="22"/>
+    </row>
+    <row r="739" spans="5:14" ht="13.2">
+      <c r="E739" s="22"/>
+      <c r="N739" s="22"/>
+    </row>
+    <row r="740" spans="5:14" ht="13.2">
+      <c r="E740" s="22"/>
+      <c r="N740" s="22"/>
+    </row>
+    <row r="741" spans="5:14" ht="13.2">
+      <c r="E741" s="22"/>
+      <c r="N741" s="22"/>
+    </row>
+    <row r="742" spans="5:14" ht="13.2">
+      <c r="E742" s="22"/>
+      <c r="N742" s="22"/>
+    </row>
+    <row r="743" spans="5:14" ht="13.2">
+      <c r="E743" s="22"/>
+      <c r="N743" s="22"/>
+    </row>
+    <row r="744" spans="5:14" ht="13.2">
+      <c r="E744" s="22"/>
+      <c r="N744" s="22"/>
+    </row>
+    <row r="745" spans="5:14" ht="13.2">
+      <c r="E745" s="22"/>
+      <c r="N745" s="22"/>
+    </row>
+    <row r="746" spans="5:14" ht="13.2">
+      <c r="E746" s="22"/>
+      <c r="N746" s="22"/>
+    </row>
+    <row r="747" spans="5:14" ht="13.2">
+      <c r="E747" s="22"/>
+      <c r="N747" s="22"/>
+    </row>
+    <row r="748" spans="5:14" ht="13.2">
+      <c r="E748" s="22"/>
+      <c r="N748" s="22"/>
+    </row>
+    <row r="749" spans="5:14" ht="13.2">
+      <c r="E749" s="22"/>
+      <c r="N749" s="22"/>
+    </row>
+    <row r="750" spans="5:14" ht="13.2">
+      <c r="E750" s="22"/>
+      <c r="N750" s="22"/>
+    </row>
+    <row r="751" spans="5:14" ht="13.2">
+      <c r="E751" s="22"/>
+      <c r="N751" s="22"/>
+    </row>
+    <row r="752" spans="5:14" ht="13.2">
+      <c r="E752" s="22"/>
+      <c r="N752" s="22"/>
+    </row>
+    <row r="753" spans="5:14" ht="13.2">
+      <c r="E753" s="22"/>
+      <c r="N753" s="22"/>
+    </row>
+    <row r="754" spans="5:14" ht="13.2">
+      <c r="E754" s="22"/>
+      <c r="N754" s="22"/>
+    </row>
+    <row r="755" spans="5:14" ht="13.2">
+      <c r="E755" s="22"/>
+      <c r="N755" s="22"/>
+    </row>
+    <row r="756" spans="5:14" ht="13.2">
+      <c r="E756" s="22"/>
+      <c r="N756" s="22"/>
+    </row>
+    <row r="757" spans="5:14" ht="13.2">
+      <c r="E757" s="22"/>
+      <c r="N757" s="22"/>
+    </row>
+    <row r="758" spans="5:14" ht="13.2">
+      <c r="E758" s="22"/>
+      <c r="N758" s="22"/>
+    </row>
+    <row r="759" spans="5:14" ht="13.2">
+      <c r="E759" s="22"/>
+      <c r="N759" s="22"/>
+    </row>
+    <row r="760" spans="5:14" ht="13.2">
+      <c r="E760" s="22"/>
+      <c r="N760" s="22"/>
+    </row>
+    <row r="761" spans="5:14" ht="13.2">
+      <c r="E761" s="22"/>
+      <c r="N761" s="22"/>
+    </row>
+    <row r="762" spans="5:14" ht="13.2">
+      <c r="E762" s="22"/>
+      <c r="N762" s="22"/>
+    </row>
+    <row r="763" spans="5:14" ht="13.2">
+      <c r="E763" s="22"/>
+      <c r="N763" s="22"/>
+    </row>
+    <row r="764" spans="5:14" ht="13.2">
+      <c r="E764" s="22"/>
+      <c r="N764" s="22"/>
+    </row>
+    <row r="765" spans="5:14" ht="13.2">
+      <c r="E765" s="22"/>
+      <c r="N765" s="22"/>
+    </row>
+    <row r="766" spans="5:14" ht="13.2">
+      <c r="E766" s="22"/>
+      <c r="N766" s="22"/>
+    </row>
+    <row r="767" spans="5:14" ht="13.2">
+      <c r="E767" s="22"/>
+      <c r="N767" s="22"/>
+    </row>
+    <row r="768" spans="5:14" ht="13.2">
+      <c r="E768" s="22"/>
+      <c r="N768" s="22"/>
+    </row>
+    <row r="769" spans="5:14" ht="13.2">
+      <c r="E769" s="22"/>
+      <c r="N769" s="22"/>
+    </row>
+    <row r="770" spans="5:14" ht="13.2">
+      <c r="E770" s="22"/>
+      <c r="N770" s="22"/>
+    </row>
+    <row r="771" spans="5:14" ht="13.2">
+      <c r="E771" s="22"/>
+      <c r="N771" s="22"/>
+    </row>
+    <row r="772" spans="5:14" ht="13.2">
+      <c r="E772" s="22"/>
+      <c r="N772" s="22"/>
+    </row>
+    <row r="773" spans="5:14" ht="13.2">
+      <c r="E773" s="22"/>
+      <c r="N773" s="22"/>
+    </row>
+    <row r="774" spans="5:14" ht="13.2">
+      <c r="E774" s="22"/>
+      <c r="N774" s="22"/>
+    </row>
+    <row r="775" spans="5:14" ht="13.2">
+      <c r="E775" s="22"/>
+      <c r="N775" s="22"/>
+    </row>
+    <row r="776" spans="5:14" ht="13.2">
+      <c r="E776" s="22"/>
+      <c r="N776" s="22"/>
+    </row>
+    <row r="777" spans="5:14" ht="13.2">
+      <c r="E777" s="22"/>
+      <c r="N777" s="22"/>
+    </row>
+    <row r="778" spans="5:14" ht="13.2">
+      <c r="E778" s="22"/>
+      <c r="N778" s="22"/>
+    </row>
+    <row r="779" spans="5:14" ht="13.2">
+      <c r="E779" s="22"/>
+      <c r="N779" s="22"/>
+    </row>
+    <row r="780" spans="5:14" ht="13.2">
+      <c r="E780" s="22"/>
+      <c r="N780" s="22"/>
+    </row>
+    <row r="781" spans="5:14" ht="13.2">
+      <c r="E781" s="22"/>
+      <c r="N781" s="22"/>
+    </row>
+    <row r="782" spans="5:14" ht="13.2">
+      <c r="E782" s="22"/>
+      <c r="N782" s="22"/>
+    </row>
+    <row r="783" spans="5:14" ht="13.2">
+      <c r="E783" s="22"/>
+      <c r="N783" s="22"/>
+    </row>
+    <row r="784" spans="5:14" ht="13.2">
+      <c r="E784" s="22"/>
+      <c r="N784" s="22"/>
+    </row>
+    <row r="785" spans="5:14" ht="13.2">
+      <c r="E785" s="22"/>
+      <c r="N785" s="22"/>
+    </row>
+    <row r="786" spans="5:14" ht="13.2">
+      <c r="E786" s="22"/>
+      <c r="N786" s="22"/>
+    </row>
+    <row r="787" spans="5:14" ht="13.2">
+      <c r="E787" s="22"/>
+      <c r="N787" s="22"/>
+    </row>
+    <row r="788" spans="5:14" ht="13.2">
+      <c r="E788" s="22"/>
+      <c r="N788" s="22"/>
+    </row>
+    <row r="789" spans="5:14" ht="13.2">
+      <c r="E789" s="22"/>
+      <c r="N789" s="22"/>
+    </row>
+    <row r="790" spans="5:14" ht="13.2">
+      <c r="E790" s="22"/>
+      <c r="N790" s="22"/>
+    </row>
+    <row r="791" spans="5:14" ht="13.2">
+      <c r="E791" s="22"/>
+      <c r="N791" s="22"/>
+    </row>
+    <row r="792" spans="5:14" ht="13.2">
+      <c r="E792" s="22"/>
+      <c r="N792" s="22"/>
+    </row>
+    <row r="793" spans="5:14" ht="13.2">
+      <c r="E793" s="22"/>
+      <c r="N793" s="22"/>
+    </row>
+    <row r="794" spans="5:14" ht="13.2">
+      <c r="E794" s="22"/>
+      <c r="N794" s="22"/>
+    </row>
+    <row r="795" spans="5:14" ht="13.2">
+      <c r="E795" s="22"/>
+      <c r="N795" s="22"/>
+    </row>
+    <row r="796" spans="5:14" ht="13.2">
+      <c r="E796" s="22"/>
+      <c r="N796" s="22"/>
+    </row>
+    <row r="797" spans="5:14" ht="13.2">
+      <c r="E797" s="22"/>
+      <c r="N797" s="22"/>
+    </row>
+    <row r="798" spans="5:14" ht="13.2">
+      <c r="E798" s="22"/>
+      <c r="N798" s="22"/>
+    </row>
+    <row r="799" spans="5:14" ht="13.2">
+      <c r="E799" s="22"/>
+      <c r="N799" s="22"/>
+    </row>
+    <row r="800" spans="5:14" ht="13.2">
+      <c r="E800" s="22"/>
+      <c r="N800" s="22"/>
+    </row>
+    <row r="801" spans="5:14" ht="13.2">
+      <c r="E801" s="22"/>
+      <c r="N801" s="22"/>
+    </row>
+    <row r="802" spans="5:14" ht="13.2">
+      <c r="E802" s="22"/>
+      <c r="N802" s="22"/>
+    </row>
+    <row r="803" spans="5:14" ht="13.2">
+      <c r="E803" s="22"/>
+      <c r="N803" s="22"/>
+    </row>
+    <row r="804" spans="5:14" ht="13.2">
+      <c r="E804" s="22"/>
+      <c r="N804" s="22"/>
+    </row>
+    <row r="805" spans="5:14" ht="13.2">
+      <c r="E805" s="22"/>
+      <c r="N805" s="22"/>
+    </row>
+    <row r="806" spans="5:14" ht="13.2">
+      <c r="E806" s="22"/>
+      <c r="N806" s="22"/>
+    </row>
+    <row r="807" spans="5:14" ht="13.2">
+      <c r="E807" s="22"/>
+      <c r="N807" s="22"/>
+    </row>
+    <row r="808" spans="5:14" ht="13.2">
+      <c r="E808" s="22"/>
+      <c r="N808" s="22"/>
+    </row>
+    <row r="809" spans="5:14" ht="13.2">
+      <c r="E809" s="22"/>
+      <c r="N809" s="22"/>
+    </row>
+    <row r="810" spans="5:14" ht="13.2">
+      <c r="E810" s="22"/>
+      <c r="N810" s="22"/>
+    </row>
+    <row r="811" spans="5:14" ht="13.2">
+      <c r="E811" s="22"/>
+      <c r="N811" s="22"/>
+    </row>
+    <row r="812" spans="5:14" ht="13.2">
+      <c r="E812" s="22"/>
+      <c r="N812" s="22"/>
+    </row>
+    <row r="813" spans="5:14" ht="13.2">
+      <c r="E813" s="22"/>
+      <c r="N813" s="22"/>
+    </row>
+    <row r="814" spans="5:14" ht="13.2">
+      <c r="E814" s="22"/>
+      <c r="N814" s="22"/>
+    </row>
+    <row r="815" spans="5:14" ht="13.2">
+      <c r="E815" s="22"/>
+      <c r="N815" s="22"/>
+    </row>
+    <row r="816" spans="5:14" ht="13.2">
+      <c r="E816" s="22"/>
+      <c r="N816" s="22"/>
+    </row>
+    <row r="817" spans="5:14" ht="13.2">
+      <c r="E817" s="22"/>
+      <c r="N817" s="22"/>
+    </row>
+    <row r="818" spans="5:14" ht="13.2">
+      <c r="E818" s="22"/>
+      <c r="N818" s="22"/>
+    </row>
+    <row r="819" spans="5:14" ht="13.2">
+      <c r="E819" s="22"/>
+      <c r="N819" s="22"/>
+    </row>
+    <row r="820" spans="5:14" ht="13.2">
+      <c r="E820" s="22"/>
+      <c r="N820" s="22"/>
+    </row>
+    <row r="821" spans="5:14" ht="13.2">
+      <c r="E821" s="22"/>
+      <c r="N821" s="22"/>
+    </row>
+    <row r="822" spans="5:14" ht="13.2">
+      <c r="E822" s="22"/>
+      <c r="N822" s="22"/>
+    </row>
+    <row r="823" spans="5:14" ht="13.2">
+      <c r="E823" s="22"/>
+      <c r="N823" s="22"/>
+    </row>
+    <row r="824" spans="5:14" ht="13.2">
+      <c r="E824" s="22"/>
+      <c r="N824" s="22"/>
+    </row>
+    <row r="825" spans="5:14" ht="13.2">
+      <c r="E825" s="22"/>
+      <c r="N825" s="22"/>
+    </row>
+    <row r="826" spans="5:14" ht="13.2">
+      <c r="E826" s="22"/>
+      <c r="N826" s="22"/>
+    </row>
+    <row r="827" spans="5:14" ht="13.2">
+      <c r="E827" s="22"/>
+      <c r="N827" s="22"/>
+    </row>
+    <row r="828" spans="5:14" ht="13.2">
+      <c r="E828" s="22"/>
+      <c r="N828" s="22"/>
+    </row>
+    <row r="829" spans="5:14" ht="13.2">
+      <c r="E829" s="22"/>
+      <c r="N829" s="22"/>
+    </row>
+    <row r="830" spans="5:14" ht="13.2">
+      <c r="E830" s="22"/>
+      <c r="N830" s="22"/>
+    </row>
+    <row r="831" spans="5:14" ht="13.2">
+      <c r="E831" s="22"/>
+      <c r="N831" s="22"/>
+    </row>
+    <row r="832" spans="5:14" ht="13.2">
+      <c r="E832" s="22"/>
+      <c r="N832" s="22"/>
+    </row>
+    <row r="833" spans="5:14" ht="13.2">
+      <c r="E833" s="22"/>
+      <c r="N833" s="22"/>
+    </row>
+    <row r="834" spans="5:14" ht="13.2">
+      <c r="E834" s="22"/>
+      <c r="N834" s="22"/>
+    </row>
+    <row r="835" spans="5:14" ht="13.2">
+      <c r="E835" s="22"/>
+      <c r="N835" s="22"/>
+    </row>
+    <row r="836" spans="5:14" ht="13.2">
+      <c r="E836" s="22"/>
+      <c r="N836" s="22"/>
+    </row>
+    <row r="837" spans="5:14" ht="13.2">
+      <c r="E837" s="22"/>
+      <c r="N837" s="22"/>
+    </row>
+    <row r="838" spans="5:14" ht="13.2">
+      <c r="E838" s="22"/>
+      <c r="N838" s="22"/>
+    </row>
+    <row r="839" spans="5:14" ht="13.2">
+      <c r="E839" s="22"/>
+      <c r="N839" s="22"/>
+    </row>
+    <row r="840" spans="5:14" ht="13.2">
+      <c r="E840" s="22"/>
+      <c r="N840" s="22"/>
+    </row>
+    <row r="841" spans="5:14" ht="13.2">
+      <c r="E841" s="22"/>
+      <c r="N841" s="22"/>
+    </row>
+    <row r="842" spans="5:14" ht="13.2">
+      <c r="E842" s="22"/>
+      <c r="N842" s="22"/>
+    </row>
+    <row r="843" spans="5:14" ht="13.2">
+      <c r="E843" s="22"/>
+      <c r="N843" s="22"/>
+    </row>
+    <row r="844" spans="5:14" ht="13.2">
+      <c r="E844" s="22"/>
+      <c r="N844" s="22"/>
+    </row>
+    <row r="845" spans="5:14" ht="13.2">
+      <c r="E845" s="22"/>
+      <c r="N845" s="22"/>
+    </row>
+    <row r="846" spans="5:14" ht="13.2">
+      <c r="E846" s="22"/>
+      <c r="N846" s="22"/>
+    </row>
+    <row r="847" spans="5:14" ht="13.2">
+      <c r="E847" s="22"/>
+      <c r="N847" s="22"/>
+    </row>
+    <row r="848" spans="5:14" ht="13.2">
+      <c r="E848" s="22"/>
+      <c r="N848" s="22"/>
+    </row>
+    <row r="849" spans="5:14" ht="13.2">
+      <c r="E849" s="22"/>
+      <c r="N849" s="22"/>
+    </row>
+    <row r="850" spans="5:14" ht="13.2">
+      <c r="E850" s="22"/>
+      <c r="N850" s="22"/>
+    </row>
+    <row r="851" spans="5:14" ht="13.2">
+      <c r="E851" s="22"/>
+      <c r="N851" s="22"/>
+    </row>
+    <row r="852" spans="5:14" ht="13.2">
+      <c r="E852" s="22"/>
+      <c r="N852" s="22"/>
+    </row>
+    <row r="853" spans="5:14" ht="13.2">
+      <c r="E853" s="22"/>
+      <c r="N853" s="22"/>
+    </row>
+    <row r="854" spans="5:14" ht="13.2">
+      <c r="E854" s="22"/>
+      <c r="N854" s="22"/>
+    </row>
+    <row r="855" spans="5:14" ht="13.2">
+      <c r="E855" s="22"/>
+      <c r="N855" s="22"/>
+    </row>
+    <row r="856" spans="5:14" ht="13.2">
+      <c r="E856" s="22"/>
+      <c r="N856" s="22"/>
+    </row>
+    <row r="857" spans="5:14" ht="13.2">
+      <c r="E857" s="22"/>
+      <c r="N857" s="22"/>
+    </row>
+    <row r="858" spans="5:14" ht="13.2">
+      <c r="E858" s="22"/>
+      <c r="N858" s="22"/>
+    </row>
+    <row r="859" spans="5:14" ht="13.2">
+      <c r="E859" s="22"/>
+      <c r="N859" s="22"/>
+    </row>
+    <row r="860" spans="5:14" ht="13.2">
+      <c r="E860" s="22"/>
+      <c r="N860" s="22"/>
+    </row>
+    <row r="861" spans="5:14" ht="13.2">
+      <c r="E861" s="22"/>
+      <c r="N861" s="22"/>
+    </row>
+    <row r="862" spans="5:14" ht="13.2">
+      <c r="E862" s="22"/>
+      <c r="N862" s="22"/>
+    </row>
+    <row r="863" spans="5:14" ht="13.2">
+      <c r="E863" s="22"/>
+      <c r="N863" s="22"/>
+    </row>
+    <row r="864" spans="5:14" ht="13.2">
+      <c r="E864" s="22"/>
+      <c r="N864" s="22"/>
+    </row>
+    <row r="865" spans="5:14" ht="13.2">
+      <c r="E865" s="22"/>
+      <c r="N865" s="22"/>
+    </row>
+    <row r="866" spans="5:14" ht="13.2">
+      <c r="E866" s="22"/>
+      <c r="N866" s="22"/>
+    </row>
+    <row r="867" spans="5:14" ht="13.2">
+      <c r="E867" s="22"/>
+      <c r="N867" s="22"/>
+    </row>
+    <row r="868" spans="5:14" ht="13.2">
+      <c r="E868" s="22"/>
+      <c r="N868" s="22"/>
+    </row>
+    <row r="869" spans="5:14" ht="13.2">
+      <c r="E869" s="22"/>
+      <c r="N869" s="22"/>
+    </row>
+    <row r="870" spans="5:14" ht="13.2">
+      <c r="E870" s="22"/>
+      <c r="N870" s="22"/>
+    </row>
+    <row r="871" spans="5:14" ht="13.2">
+      <c r="E871" s="22"/>
+      <c r="N871" s="22"/>
+    </row>
+    <row r="872" spans="5:14" ht="13.2">
+      <c r="E872" s="22"/>
+      <c r="N872" s="22"/>
+    </row>
+    <row r="873" spans="5:14" ht="13.2">
+      <c r="E873" s="22"/>
+      <c r="N873" s="22"/>
+    </row>
+    <row r="874" spans="5:14" ht="13.2">
+      <c r="E874" s="22"/>
+      <c r="N874" s="22"/>
+    </row>
+    <row r="875" spans="5:14" ht="13.2">
+      <c r="E875" s="22"/>
+      <c r="N875" s="22"/>
+    </row>
+    <row r="876" spans="5:14" ht="13.2">
+      <c r="E876" s="22"/>
+      <c r="N876" s="22"/>
+    </row>
+    <row r="877" spans="5:14" ht="13.2">
+      <c r="E877" s="22"/>
+      <c r="N877" s="22"/>
+    </row>
+    <row r="878" spans="5:14" ht="13.2">
+      <c r="E878" s="22"/>
+      <c r="N878" s="22"/>
+    </row>
+    <row r="879" spans="5:14" ht="13.2">
+      <c r="E879" s="22"/>
+      <c r="N879" s="22"/>
+    </row>
+    <row r="880" spans="5:14" ht="13.2">
+      <c r="E880" s="22"/>
+      <c r="N880" s="22"/>
+    </row>
+    <row r="881" spans="5:14" ht="13.2">
+      <c r="E881" s="22"/>
+      <c r="N881" s="22"/>
+    </row>
+    <row r="882" spans="5:14" ht="13.2">
+      <c r="E882" s="22"/>
+      <c r="N882" s="22"/>
+    </row>
+    <row r="883" spans="5:14" ht="13.2">
+      <c r="E883" s="22"/>
+      <c r="N883" s="22"/>
+    </row>
+    <row r="884" spans="5:14" ht="13.2">
+      <c r="E884" s="22"/>
+      <c r="N884" s="22"/>
+    </row>
+    <row r="885" spans="5:14" ht="13.2">
+      <c r="E885" s="22"/>
+      <c r="N885" s="22"/>
+    </row>
+    <row r="886" spans="5:14" ht="13.2">
+      <c r="E886" s="22"/>
+      <c r="N886" s="22"/>
+    </row>
+    <row r="887" spans="5:14" ht="13.2">
+      <c r="E887" s="22"/>
+      <c r="N887" s="22"/>
+    </row>
+    <row r="888" spans="5:14" ht="13.2">
+      <c r="E888" s="22"/>
+      <c r="N888" s="22"/>
+    </row>
+    <row r="889" spans="5:14" ht="13.2">
+      <c r="E889" s="22"/>
+      <c r="N889" s="22"/>
+    </row>
+    <row r="890" spans="5:14" ht="13.2">
+      <c r="E890" s="22"/>
+      <c r="N890" s="22"/>
+    </row>
+    <row r="891" spans="5:14" ht="13.2">
+      <c r="E891" s="22"/>
+      <c r="N891" s="22"/>
+    </row>
+    <row r="892" spans="5:14" ht="13.2">
+      <c r="E892" s="22"/>
+      <c r="N892" s="22"/>
+    </row>
+    <row r="893" spans="5:14" ht="13.2">
+      <c r="E893" s="22"/>
+      <c r="N893" s="22"/>
+    </row>
+    <row r="894" spans="5:14" ht="13.2">
+      <c r="E894" s="22"/>
+      <c r="N894" s="22"/>
+    </row>
+    <row r="895" spans="5:14" ht="13.2">
+      <c r="E895" s="22"/>
+      <c r="N895" s="22"/>
+    </row>
+    <row r="896" spans="5:14" ht="13.2">
+      <c r="E896" s="22"/>
+      <c r="N896" s="22"/>
+    </row>
+    <row r="897" spans="5:14" ht="13.2">
+      <c r="E897" s="22"/>
+      <c r="N897" s="22"/>
+    </row>
+    <row r="898" spans="5:14" ht="13.2">
+      <c r="E898" s="22"/>
+      <c r="N898" s="22"/>
+    </row>
+    <row r="899" spans="5:14" ht="13.2">
+      <c r="E899" s="22"/>
+      <c r="N899" s="22"/>
+    </row>
+    <row r="900" spans="5:14" ht="13.2">
+      <c r="E900" s="22"/>
+      <c r="N900" s="22"/>
+    </row>
+    <row r="901" spans="5:14" ht="13.2">
+      <c r="E901" s="22"/>
+      <c r="N901" s="22"/>
+    </row>
+    <row r="902" spans="5:14" ht="13.2">
+      <c r="E902" s="22"/>
+      <c r="N902" s="22"/>
+    </row>
+    <row r="903" spans="5:14" ht="13.2">
+      <c r="E903" s="22"/>
+      <c r="N903" s="22"/>
+    </row>
+    <row r="904" spans="5:14" ht="13.2">
+      <c r="E904" s="22"/>
+      <c r="N904" s="22"/>
+    </row>
+    <row r="905" spans="5:14" ht="13.2">
+      <c r="E905" s="22"/>
+      <c r="N905" s="22"/>
+    </row>
+    <row r="906" spans="5:14" ht="13.2">
+      <c r="E906" s="22"/>
+      <c r="N906" s="22"/>
+    </row>
+    <row r="907" spans="5:14" ht="13.2">
+      <c r="E907" s="22"/>
+      <c r="N907" s="22"/>
+    </row>
+    <row r="908" spans="5:14" ht="13.2">
+      <c r="E908" s="22"/>
+      <c r="N908" s="22"/>
+    </row>
+    <row r="909" spans="5:14" ht="13.2">
+      <c r="E909" s="22"/>
+      <c r="N909" s="22"/>
+    </row>
+    <row r="910" spans="5:14" ht="13.2">
+      <c r="E910" s="22"/>
+      <c r="N910" s="22"/>
+    </row>
+    <row r="911" spans="5:14" ht="13.2">
+      <c r="E911" s="22"/>
+      <c r="N911" s="22"/>
+    </row>
+    <row r="912" spans="5:14" ht="13.2">
+      <c r="E912" s="22"/>
+      <c r="N912" s="22"/>
+    </row>
+    <row r="913" spans="5:14" ht="13.2">
+      <c r="E913" s="22"/>
+      <c r="N913" s="22"/>
+    </row>
+    <row r="914" spans="5:14" ht="13.2">
+      <c r="E914" s="22"/>
+      <c r="N914" s="22"/>
+    </row>
+    <row r="915" spans="5:14" ht="13.2">
+      <c r="E915" s="22"/>
+      <c r="N915" s="22"/>
+    </row>
+    <row r="916" spans="5:14" ht="13.2">
+      <c r="E916" s="22"/>
+      <c r="N916" s="22"/>
+    </row>
+    <row r="917" spans="5:14" ht="13.2">
+      <c r="E917" s="22"/>
+      <c r="N917" s="22"/>
+    </row>
+    <row r="918" spans="5:14" ht="13.2">
+      <c r="E918" s="22"/>
+      <c r="N918" s="22"/>
+    </row>
+    <row r="919" spans="5:14" ht="13.2">
+      <c r="E919" s="22"/>
+      <c r="N919" s="22"/>
+    </row>
+    <row r="920" spans="5:14" ht="13.2">
+      <c r="E920" s="22"/>
+      <c r="N920" s="22"/>
+    </row>
+    <row r="921" spans="5:14" ht="13.2">
+      <c r="E921" s="22"/>
+      <c r="N921" s="22"/>
+    </row>
+    <row r="922" spans="5:14" ht="13.2">
+      <c r="E922" s="22"/>
+      <c r="N922" s="22"/>
+    </row>
+    <row r="923" spans="5:14" ht="13.2">
+      <c r="E923" s="22"/>
+      <c r="N923" s="22"/>
+    </row>
+    <row r="924" spans="5:14" ht="13.2">
+      <c r="E924" s="22"/>
+      <c r="N924" s="22"/>
+    </row>
+    <row r="925" spans="5:14" ht="13.2">
+      <c r="E925" s="22"/>
+      <c r="N925" s="22"/>
+    </row>
+    <row r="926" spans="5:14" ht="13.2">
+      <c r="E926" s="22"/>
+      <c r="N926" s="22"/>
+    </row>
+    <row r="927" spans="5:14" ht="13.2">
+      <c r="E927" s="22"/>
+      <c r="N927" s="22"/>
+    </row>
+    <row r="928" spans="5:14" ht="13.2">
+      <c r="E928" s="22"/>
+      <c r="N928" s="22"/>
+    </row>
+    <row r="929" spans="5:14" ht="13.2">
+      <c r="E929" s="22"/>
+      <c r="N929" s="22"/>
+    </row>
+    <row r="930" spans="5:14" ht="13.2">
+      <c r="E930" s="22"/>
+      <c r="N930" s="22"/>
+    </row>
+    <row r="931" spans="5:14" ht="13.2">
+      <c r="E931" s="22"/>
+      <c r="N931" s="22"/>
+    </row>
+    <row r="932" spans="5:14" ht="13.2">
+      <c r="E932" s="22"/>
+      <c r="N932" s="22"/>
+    </row>
+    <row r="933" spans="5:14" ht="13.2">
+      <c r="E933" s="22"/>
+      <c r="N933" s="22"/>
+    </row>
+    <row r="934" spans="5:14" ht="13.2">
+      <c r="E934" s="22"/>
+      <c r="N934" s="22"/>
+    </row>
+    <row r="935" spans="5:14" ht="13.2">
+      <c r="E935" s="22"/>
+      <c r="N935" s="22"/>
+    </row>
+    <row r="936" spans="5:14" ht="13.2">
+      <c r="E936" s="22"/>
+      <c r="N936" s="22"/>
+    </row>
+    <row r="937" spans="5:14" ht="13.2">
+      <c r="E937" s="22"/>
+      <c r="N937" s="22"/>
+    </row>
+    <row r="938" spans="5:14" ht="13.2">
+      <c r="E938" s="22"/>
+      <c r="N938" s="22"/>
+    </row>
+    <row r="939" spans="5:14" ht="13.2">
+      <c r="E939" s="22"/>
+      <c r="N939" s="22"/>
+    </row>
+    <row r="940" spans="5:14" ht="13.2">
+      <c r="E940" s="22"/>
+      <c r="N940" s="22"/>
+    </row>
+    <row r="941" spans="5:14" ht="13.2">
+      <c r="E941" s="22"/>
+      <c r="N941" s="22"/>
+    </row>
+    <row r="942" spans="5:14" ht="13.2">
+      <c r="E942" s="22"/>
+      <c r="N942" s="22"/>
+    </row>
+    <row r="943" spans="5:14" ht="13.2">
+      <c r="E943" s="22"/>
+      <c r="N943" s="22"/>
+    </row>
+    <row r="944" spans="5:14" ht="13.2">
+      <c r="E944" s="22"/>
+      <c r="N944" s="22"/>
+    </row>
+    <row r="945" spans="5:14" ht="13.2">
+      <c r="E945" s="22"/>
+      <c r="N945" s="22"/>
+    </row>
+    <row r="946" spans="5:14" ht="13.2">
+      <c r="E946" s="22"/>
+      <c r="N946" s="22"/>
+    </row>
+    <row r="947" spans="5:14" ht="13.2">
+      <c r="E947" s="22"/>
+      <c r="N947" s="22"/>
+    </row>
+    <row r="948" spans="5:14" ht="13.2">
+      <c r="E948" s="22"/>
+      <c r="N948" s="22"/>
+    </row>
+    <row r="949" spans="5:14" ht="13.2">
+      <c r="E949" s="22"/>
+      <c r="N949" s="22"/>
+    </row>
+    <row r="950" spans="5:14" ht="13.2">
+      <c r="E950" s="22"/>
+      <c r="N950" s="22"/>
+    </row>
+    <row r="951" spans="5:14" ht="13.2">
+      <c r="E951" s="22"/>
+      <c r="N951" s="22"/>
+    </row>
+    <row r="952" spans="5:14" ht="13.2">
+      <c r="E952" s="22"/>
+      <c r="N952" s="22"/>
+    </row>
+    <row r="953" spans="5:14" ht="13.2">
+      <c r="E953" s="22"/>
+      <c r="N953" s="22"/>
+    </row>
+    <row r="954" spans="5:14" ht="13.2">
+      <c r="E954" s="22"/>
+      <c r="N954" s="22"/>
+    </row>
+    <row r="955" spans="5:14" ht="13.2">
+      <c r="E955" s="22"/>
+      <c r="N955" s="22"/>
+    </row>
+    <row r="956" spans="5:14" ht="13.2">
+      <c r="E956" s="22"/>
+      <c r="N956" s="22"/>
+    </row>
+    <row r="957" spans="5:14" ht="13.2">
+      <c r="E957" s="22"/>
+      <c r="N957" s="22"/>
+    </row>
+    <row r="958" spans="5:14" ht="13.2">
+      <c r="E958" s="22"/>
+      <c r="N958" s="22"/>
+    </row>
+    <row r="959" spans="5:14" ht="13.2">
+      <c r="E959" s="22"/>
+      <c r="N959" s="22"/>
+    </row>
+    <row r="960" spans="5:14" ht="13.2">
+      <c r="E960" s="22"/>
+      <c r="N960" s="22"/>
+    </row>
+    <row r="961" spans="5:14" ht="13.2">
+      <c r="E961" s="22"/>
+      <c r="N961" s="22"/>
+    </row>
+    <row r="962" spans="5:14" ht="13.2">
+      <c r="E962" s="22"/>
+      <c r="N962" s="22"/>
+    </row>
+    <row r="963" spans="5:14" ht="13.2">
+      <c r="E963" s="22"/>
+      <c r="N963" s="22"/>
+    </row>
+    <row r="964" spans="5:14" ht="13.2">
+      <c r="E964" s="22"/>
+      <c r="N964" s="22"/>
+    </row>
+    <row r="965" spans="5:14" ht="13.2">
+      <c r="E965" s="22"/>
+      <c r="N965" s="22"/>
+    </row>
+    <row r="966" spans="5:14" ht="13.2">
+      <c r="E966" s="22"/>
+      <c r="N966" s="22"/>
+    </row>
+    <row r="967" spans="5:14" ht="13.2">
+      <c r="E967" s="22"/>
+      <c r="N967" s="22"/>
+    </row>
+    <row r="968" spans="5:14" ht="13.2">
+      <c r="E968" s="22"/>
+      <c r="N968" s="22"/>
+    </row>
+    <row r="969" spans="5:14" ht="13.2">
+      <c r="E969" s="22"/>
+      <c r="N969" s="22"/>
+    </row>
+    <row r="970" spans="5:14" ht="13.2">
+      <c r="E970" s="22"/>
+      <c r="N970" s="22"/>
+    </row>
+    <row r="971" spans="5:14" ht="13.2">
+      <c r="E971" s="22"/>
+      <c r="N971" s="22"/>
+    </row>
+    <row r="972" spans="5:14" ht="13.2">
+      <c r="E972" s="22"/>
+      <c r="N972" s="22"/>
+    </row>
+    <row r="973" spans="5:14" ht="13.2">
+      <c r="E973" s="22"/>
+      <c r="N973" s="22"/>
+    </row>
+    <row r="974" spans="5:14" ht="13.2">
+      <c r="E974" s="22"/>
+      <c r="N974" s="22"/>
+    </row>
+    <row r="975" spans="5:14" ht="13.2">
+      <c r="E975" s="22"/>
+      <c r="N975" s="22"/>
+    </row>
+    <row r="976" spans="5:14" ht="13.2">
+      <c r="E976" s="22"/>
+      <c r="N976" s="22"/>
+    </row>
+    <row r="977" spans="5:14" ht="13.2">
+      <c r="E977" s="22"/>
+      <c r="N977" s="22"/>
+    </row>
+    <row r="978" spans="5:14" ht="13.2">
+      <c r="E978" s="22"/>
+      <c r="N978" s="22"/>
+    </row>
+    <row r="979" spans="5:14" ht="13.2">
+      <c r="E979" s="22"/>
+      <c r="N979" s="22"/>
+    </row>
+    <row r="980" spans="5:14" ht="13.2">
+      <c r="E980" s="22"/>
+      <c r="N980" s="22"/>
+    </row>
+    <row r="981" spans="5:14" ht="13.2">
+      <c r="E981" s="22"/>
+      <c r="N981" s="22"/>
+    </row>
+    <row r="982" spans="5:14" ht="13.2">
+      <c r="E982" s="22"/>
+      <c r="N982" s="22"/>
+    </row>
+    <row r="983" spans="5:14" ht="13.2">
+      <c r="E983" s="22"/>
+      <c r="N983" s="22"/>
+    </row>
+    <row r="984" spans="5:14" ht="13.2">
+      <c r="E984" s="22"/>
+      <c r="N984" s="22"/>
+    </row>
+    <row r="985" spans="5:14" ht="13.2">
+      <c r="E985" s="22"/>
+      <c r="N985" s="22"/>
+    </row>
+    <row r="986" spans="5:14" ht="13.2">
+      <c r="E986" s="22"/>
+      <c r="N986" s="22"/>
+    </row>
+    <row r="987" spans="5:14" ht="13.2">
+      <c r="E987" s="22"/>
+      <c r="N987" s="22"/>
+    </row>
+    <row r="988" spans="5:14" ht="13.2">
+      <c r="E988" s="22"/>
+      <c r="N988" s="22"/>
+    </row>
+    <row r="989" spans="5:14" ht="13.2">
+      <c r="E989" s="22"/>
+      <c r="N989" s="22"/>
+    </row>
+    <row r="990" spans="5:14" ht="13.2">
+      <c r="E990" s="22"/>
+      <c r="N990" s="22"/>
+    </row>
+    <row r="991" spans="5:14" ht="13.2">
+      <c r="E991" s="22"/>
+      <c r="N991" s="22"/>
+    </row>
+    <row r="992" spans="5:14" ht="13.2">
+      <c r="E992" s="22"/>
+      <c r="N992" s="22"/>
+    </row>
+    <row r="993" spans="5:14" ht="13.2">
+      <c r="E993" s="22"/>
+      <c r="N993" s="22"/>
+    </row>
+    <row r="994" spans="5:14" ht="13.2">
+      <c r="E994" s="22"/>
+      <c r="N994" s="22"/>
+    </row>
+    <row r="995" spans="5:14" ht="13.2">
+      <c r="E995" s="22"/>
+      <c r="N995" s="22"/>
+    </row>
+    <row r="996" spans="5:14" ht="13.2">
+      <c r="E996" s="22"/>
+      <c r="N996" s="22"/>
+    </row>
+    <row r="997" spans="5:14" ht="13.2">
+      <c r="E997" s="22"/>
+      <c r="N997" s="22"/>
+    </row>
+    <row r="998" spans="5:14" ht="13.2">
+      <c r="E998" s="22"/>
+      <c r="N998" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="I7"/>
-    <hyperlink r:id="rId2" ref="I8"/>
+    <hyperlink ref="I7" r:id="rId1"/>
+    <hyperlink ref="I8" r:id="rId2"/>
+    <hyperlink ref="I9" r:id="rId3"/>
+    <hyperlink ref="I10" r:id="rId4"/>
+    <hyperlink ref="I11" r:id="rId5"/>
+    <hyperlink ref="I12" r:id="rId6"/>
+    <hyperlink ref="I13" r:id="rId7"/>
+    <hyperlink ref="I14" r:id="rId8"/>
+    <hyperlink ref="I15" r:id="rId9"/>
+    <hyperlink ref="I16" r:id="rId10"/>
   </hyperlinks>
-  <drawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>